--- a/results-summarized/summary-Irish-xsk.xlsx
+++ b/results-summarized/summary-Irish-xsk.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kowk/Dropbox/GitHub/ngram-based-noun-classification/results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kowk/Dropbox/GitHub/ngram-based-noun-classification/results-summarized/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A57EED-639A-0347-AD5D-9A893DF18407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548BFCB8-ED49-F345-81D1-B827DF8ABC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="1760" windowWidth="36760" windowHeight="19120" activeTab="3" xr2:uid="{71B4F2C9-6E63-8A4B-9DCD-9E067D82C8E5}"/>
+    <workbookView xWindow="9200" yWindow="1040" windowWidth="25940" windowHeight="17700" activeTab="9" xr2:uid="{71B4F2C9-6E63-8A4B-9DCD-9E067D82C8E5}"/>
   </bookViews>
   <sheets>
     <sheet name="summarized" sheetId="21" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="44">
   <si>
     <t>lang</t>
   </si>
@@ -10284,7 +10284,7 @@
     <tableColumn id="2" xr3:uid="{A3824ECA-2A1D-8741-83E5-6290AC873E2A}" name="attribute"/>
     <tableColumn id="3" xr3:uid="{7BBD7B86-2074-B645-8524-238F50D3DE6D}" name="supplemented"/>
     <tableColumn id="4" xr3:uid="{9E10590C-C913-EA4E-9E98-7156913BCA27}" name="method.index"/>
-    <tableColumn id="5" xr3:uid="{6F9F18C4-B256-C148-98D4-4B29EB1D2433}" name="metric"/>
+    <tableColumn id="5" xr3:uid="{6F9F18C4-B256-C148-98D4-4B29EB1D2433}" name="method"/>
     <tableColumn id="6" xr3:uid="{2515FB97-A4BC-3249-B81F-D2ED8E7B8984}" name="2g-no-hash" dataDxfId="209">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
@@ -10481,18 +10481,19 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{5E48912A-7CC9-DF4C-BA51-9A5971D3A22B}" name="Table9" displayName="Table9" ref="A1:S19" totalsRowShown="0">
-  <autoFilter ref="A1:S19" xr:uid="{5E48912A-7CC9-DF4C-BA51-9A5971D3A22B}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{5E48912A-7CC9-DF4C-BA51-9A5971D3A22B}" name="Table9" displayName="Table9" ref="A1:T19" totalsRowShown="0">
+  <autoFilter ref="A1:T19" xr:uid="{5E48912A-7CC9-DF4C-BA51-9A5971D3A22B}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T19">
     <sortCondition ref="B1:B19"/>
   </sortState>
-  <tableColumns count="19">
+  <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{6C03FD0A-DD42-4D45-ACB4-A477BEF1C07A}" name="lang"/>
     <tableColumn id="2" xr3:uid="{D817D229-DC9F-134E-8928-BBF977BCE971}" name="attribute.index"/>
     <tableColumn id="3" xr3:uid="{A4A64A1C-37F5-2148-860E-AB14E6C29D96}" name="attribute"/>
     <tableColumn id="4" xr3:uid="{DF526215-4A60-9E47-BB3B-DBEF86408162}" name="supplement"/>
     <tableColumn id="5" xr3:uid="{3013F12A-D0CE-8741-A18C-EEC129C05A97}" name="method.index"/>
     <tableColumn id="6" xr3:uid="{1C06CC11-EB29-E246-BDE3-21AD20ED8A9C}" name="method"/>
+    <tableColumn id="20" xr3:uid="{CF3FD2B8-AB0B-A741-BEE2-069A3CF97611}" name="var"/>
     <tableColumn id="7" xr3:uid="{2D030BEB-FF4A-8240-A854-AF30F1BE183F}" name="2g-no-hash" dataDxfId="155"/>
     <tableColumn id="8" xr3:uid="{525D4CD1-24DA-9C48-94E4-0B1ABC9BF6BD}" name="3g-no-hash" dataDxfId="154"/>
     <tableColumn id="9" xr3:uid="{A01B788D-8235-DA4F-8392-5F740710EF90}" name="4g-no-hash" dataDxfId="153"/>
@@ -10506,7 +10507,7 @@
     <tableColumn id="17" xr3:uid="{282CFDBF-A0E8-6D4D-818A-3335D50FF33B}" name="xsk3g-hash-at-both" dataDxfId="145"/>
     <tableColumn id="18" xr3:uid="{8835329B-2D79-3B46-9E73-48D728F2B87F}" name="xsk4g-hash-at-both" dataDxfId="144"/>
     <tableColumn id="19" xr3:uid="{1B41A665-73E4-2C41-8ABA-61C4859A6634}" name="max" dataDxfId="143">
-      <calculatedColumnFormula>MAX($G2:$R2)</calculatedColumnFormula>
+      <calculatedColumnFormula>MAX($H2:$S2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -10514,52 +10515,53 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{FDFF999A-7635-A047-BDFC-D157F9312BD9}" name="Table611" displayName="Table611" ref="B22:S28" totalsRowShown="0">
-  <autoFilter ref="B22:S28" xr:uid="{FDFF999A-7635-A047-BDFC-D157F9312BD9}"/>
-  <tableColumns count="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{FDFF999A-7635-A047-BDFC-D157F9312BD9}" name="Table611" displayName="Table611" ref="B22:T28" totalsRowShown="0">
+  <autoFilter ref="B22:T28" xr:uid="{FDFF999A-7635-A047-BDFC-D157F9312BD9}"/>
+  <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{0A40F905-960F-B043-A2CA-CAF5BFE33ED7}" name="attribute.index"/>
     <tableColumn id="2" xr3:uid="{9ED09634-2354-E647-B48F-B53810D0F367}" name="attribute"/>
     <tableColumn id="3" xr3:uid="{A18358F4-43EE-B544-8713-C747FFEC9592}" name="supplemented"/>
     <tableColumn id="4" xr3:uid="{8A419190-E2E2-6345-A784-646A9249877E}" name="method.index"/>
-    <tableColumn id="5" xr3:uid="{CA38F21C-B15B-E74E-8578-3E8C4273773E}" name="metric"/>
+    <tableColumn id="5" xr3:uid="{CA38F21C-B15B-E74E-8578-3E8C4273773E}" name="method"/>
+    <tableColumn id="19" xr3:uid="{233B9A09-46F6-E64C-AF30-BC4F086AEEA6}" name="var"/>
     <tableColumn id="6" xr3:uid="{8517EA3B-862F-1D47-8999-4C0059CB0E38}" name="2g-no-hash" dataDxfId="142">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{903471C2-4783-0A40-9202-544F77D59C65}" name="3g-no-hash" dataDxfId="141">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{A4C98190-859D-1248-8DEC-B7AA1F54313A}" name="4g-no-hash" dataDxfId="140">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{26778D2F-829B-A44E-B99E-12406DBFEDFC}" name="sk2g-no-hash" dataDxfId="139">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{AE07F32D-E181-8A4E-8F38-45B5127A6A98}" name="sk3g-no-hash" dataDxfId="138">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="11" xr3:uid="{6C847397-02F9-9F41-8B34-9AEB3E33CFC1}" name="sk4g-no-hash" dataDxfId="137">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{ACAB7089-F2D2-A144-B006-3268C4BCB30B}" name="2g-hash-at-both" dataDxfId="136">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="13" xr3:uid="{54164F9C-ED2C-5747-B55A-5657A8461F4C}" name="3g-hash-at-both" dataDxfId="135">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="14" xr3:uid="{02AE129B-70F7-CA4E-AF8F-329898E4D0EC}" name="4g-hash-at-both" dataDxfId="134">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="15" xr3:uid="{5C53EE3C-5042-3D41-84B0-05FDF5A21F5E}" name="sk2g-hash-at-both" dataDxfId="133">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{6B758EE9-E2A5-FA40-8450-9EB7C7826937}" name="sk3g-hash-at-both" dataDxfId="132">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="17" xr3:uid="{E77023D9-A51A-6E48-A8AA-16CBCBB0966C}" name="sk4g-hash-at-both" dataDxfId="131">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="18" xr3:uid="{6E60272A-AB1A-B047-8CA3-9AFCE6B4776F}" name="max" dataDxfId="130">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -10607,7 +10609,7 @@
     <tableColumn id="2" xr3:uid="{16D72E46-7740-F34E-BA6A-7CDFD600CC02}" name="attribute"/>
     <tableColumn id="3" xr3:uid="{1873A61C-6728-F349-B7C0-27DF172E4D56}" name="supplemented"/>
     <tableColumn id="4" xr3:uid="{FD5DD7A1-560D-0448-AEFD-BFC9E1755B71}" name="method.index"/>
-    <tableColumn id="5" xr3:uid="{DD4863BE-0A81-D24D-A593-FDCE9CC6BA6D}" name="metric"/>
+    <tableColumn id="5" xr3:uid="{DD4863BE-0A81-D24D-A593-FDCE9CC6BA6D}" name="method"/>
     <tableColumn id="6" xr3:uid="{C1D49DF9-37D6-9B49-99ED-DF4CA8EBB479}" name="2g-no-hash" dataDxfId="116">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
@@ -10693,7 +10695,7 @@
     <tableColumn id="2" xr3:uid="{36B3C356-3935-7F44-A2E6-166CBFDAFA8D}" name="attribute"/>
     <tableColumn id="3" xr3:uid="{19F26803-DE93-1847-8ABB-B568FF269A5A}" name="supplemented"/>
     <tableColumn id="4" xr3:uid="{E8038C3E-9120-8948-8113-24EF0FF09128}" name="method.index"/>
-    <tableColumn id="5" xr3:uid="{DE5228A8-4D92-E54B-8C95-FD8B616974C5}" name="metric"/>
+    <tableColumn id="5" xr3:uid="{DE5228A8-4D92-E54B-8C95-FD8B616974C5}" name="method"/>
     <tableColumn id="6" xr3:uid="{5003594A-4035-9B48-A6D1-DDF757E59514}" name="2g-no-hash" dataDxfId="90">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
@@ -10757,18 +10759,19 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{47CC56E2-3597-8248-BD5F-D93F4622F12F}" name="Table21" displayName="Table21" ref="A1:S19" totalsRowShown="0">
-  <autoFilter ref="A1:S19" xr:uid="{47CC56E2-3597-8248-BD5F-D93F4622F12F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{47CC56E2-3597-8248-BD5F-D93F4622F12F}" name="Table21" displayName="Table21" ref="A1:T19" totalsRowShown="0">
+  <autoFilter ref="A1:T19" xr:uid="{47CC56E2-3597-8248-BD5F-D93F4622F12F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T19">
     <sortCondition ref="B1:B19"/>
   </sortState>
-  <tableColumns count="19">
+  <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{EAFF58FB-C5C1-5040-B33C-48F14F31B35F}" name="lang"/>
     <tableColumn id="2" xr3:uid="{ED68D77A-3068-F549-B836-7B015B607604}" name="attribute.index"/>
     <tableColumn id="3" xr3:uid="{C74B6E78-FDC4-724E-8A32-936F62BB252D}" name="attribute"/>
     <tableColumn id="4" xr3:uid="{C865FCE8-EC7E-E547-85E3-CA79AEC67C51}" name="supplement"/>
     <tableColumn id="5" xr3:uid="{CA761ECA-86F0-FA4F-BE41-3CFF3C7CB699}" name="method.index"/>
     <tableColumn id="6" xr3:uid="{682E7AF5-6860-C149-996F-993134127EA7}" name="method"/>
+    <tableColumn id="20" xr3:uid="{7C2D4493-3676-9845-A38B-B6E3CAB06915}" name="var"/>
     <tableColumn id="7" xr3:uid="{051FE646-E2D0-FB46-ACF0-EB7515978BD0}" name="2g-no-hash" dataDxfId="77"/>
     <tableColumn id="8" xr3:uid="{34E694F7-0ECB-3445-AA62-8FF973AB75CE}" name="3g-no-hash" dataDxfId="76"/>
     <tableColumn id="9" xr3:uid="{27636680-8B60-294E-A9DC-E25BBF3E9B4B}" name="4g-no-hash" dataDxfId="75"/>
@@ -10782,7 +10785,7 @@
     <tableColumn id="17" xr3:uid="{83A29C06-C0BD-FF4E-BA92-452D3883A049}" name="xsk3g-hash-at-both" dataDxfId="67"/>
     <tableColumn id="18" xr3:uid="{7B88A0F0-C1DC-7D46-9EEB-B801747DB5E4}" name="xsk4g-hash-at-both" dataDxfId="66"/>
     <tableColumn id="19" xr3:uid="{D55F462A-D507-8F49-9BB7-9676996448E0}" name="max" dataDxfId="65">
-      <calculatedColumnFormula>MAX($G2:$R2)</calculatedColumnFormula>
+      <calculatedColumnFormula>MAX($H2:$S2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -10790,52 +10793,53 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{DFEC8141-C2E7-9B49-A300-75F37CA12603}" name="Table623" displayName="Table623" ref="B22:S28" totalsRowShown="0">
-  <autoFilter ref="B22:S28" xr:uid="{DFEC8141-C2E7-9B49-A300-75F37CA12603}"/>
-  <tableColumns count="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{DFEC8141-C2E7-9B49-A300-75F37CA12603}" name="Table623" displayName="Table623" ref="B22:T28" totalsRowShown="0">
+  <autoFilter ref="B22:T28" xr:uid="{DFEC8141-C2E7-9B49-A300-75F37CA12603}"/>
+  <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{4D07919E-A1E2-AD41-9613-AB70B51BA9AF}" name="attribute.index"/>
     <tableColumn id="2" xr3:uid="{FFED1251-0751-D040-8FA9-E61DAF1E5324}" name="attribute"/>
     <tableColumn id="3" xr3:uid="{437993F4-3538-7045-9AB9-ABD6F4F85391}" name="supplemented"/>
     <tableColumn id="4" xr3:uid="{22FF023C-B9FF-E242-8000-0FF1041496B6}" name="method.index"/>
-    <tableColumn id="5" xr3:uid="{E0F1DF98-7130-1642-9F71-55870FF746C1}" name="metric"/>
+    <tableColumn id="5" xr3:uid="{E0F1DF98-7130-1642-9F71-55870FF746C1}" name="method"/>
+    <tableColumn id="19" xr3:uid="{7F5D5191-FD6E-FF4A-98C5-D3A0111804E1}" name="var"/>
     <tableColumn id="6" xr3:uid="{5C1B5263-D601-1B47-A206-D3F7169EF4A0}" name="2g-no-hash" dataDxfId="64">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{31A4296F-94CE-844B-956C-B4854E44A495}" name="3g-no-hash" dataDxfId="63">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{407686B7-19EB-3745-8F5B-C47EBC966B14}" name="4g-no-hash" dataDxfId="62">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{2EC56FE5-DBE6-6146-A9CE-30C29211A697}" name="xsk2g-no-hash" dataDxfId="61">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{0905E48D-6635-5F46-8574-41E552E87128}" name="xsk3g-no-hash" dataDxfId="60">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="11" xr3:uid="{5A2344C8-CCB5-A94E-B5E4-DE203A1DAAE2}" name="xsk4g-no-hash" dataDxfId="59">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{1562E203-798E-7046-8FEE-80F3995713BE}" name="2g-hash-at-both" dataDxfId="58">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="13" xr3:uid="{A13D5250-1DD8-814B-953A-30E9C4DC9F7F}" name="3g-hash-at-both" dataDxfId="57">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="14" xr3:uid="{E3BA6312-99A5-AB43-92A7-756C25CB6C1D}" name="4g-hash-at-both" dataDxfId="56">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="15" xr3:uid="{E9A1BEEB-787C-754C-BE97-DF419E8B97B9}" name="xsk2g-hash-at-both" dataDxfId="55">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{3A68B200-CE9B-D840-B7A1-EDC4A92B3FA2}" name="xsk3g-hash-at-both" dataDxfId="54">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="17" xr3:uid="{0DF08543-1A83-134C-9AB2-67114811C8CB}" name="xsk4g-hash-at-both" dataDxfId="53">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="18" xr3:uid="{BB3CD15E-ACB4-AC45-81A7-03AF2E61E81E}" name="max" dataDxfId="52">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -10843,18 +10847,19 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{BD7BD748-4EF8-9943-A972-3647D50ECC03}" name="Table19" displayName="Table19" ref="A1:S19" totalsRowShown="0">
-  <autoFilter ref="A1:S19" xr:uid="{BD7BD748-4EF8-9943-A972-3647D50ECC03}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{BD7BD748-4EF8-9943-A972-3647D50ECC03}" name="Table19" displayName="Table19" ref="A1:T19" totalsRowShown="0">
+  <autoFilter ref="A1:T19" xr:uid="{BD7BD748-4EF8-9943-A972-3647D50ECC03}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T19">
     <sortCondition ref="B1:B19"/>
   </sortState>
-  <tableColumns count="19">
+  <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{01554D7B-3FE8-9C49-95E7-28C65C973255}" name="lang"/>
     <tableColumn id="2" xr3:uid="{DDF13E5E-3ABD-994F-8398-5E3C3A702CA4}" name="attribute.index"/>
     <tableColumn id="3" xr3:uid="{3AD787FA-628D-9949-A749-003323038F4A}" name="attribute"/>
     <tableColumn id="4" xr3:uid="{F54ED1E3-1A3A-F94C-A99B-5BE1CBDB9B03}" name="supplement"/>
     <tableColumn id="5" xr3:uid="{D89B121F-E717-AE4D-A9FE-912764C5667C}" name="method.index"/>
     <tableColumn id="6" xr3:uid="{4E940863-2176-0941-ACA0-6D49F033DC06}" name="method"/>
+    <tableColumn id="20" xr3:uid="{78EB4DD1-801A-3942-8EF4-C623EF8B60EA}" name="var"/>
     <tableColumn id="7" xr3:uid="{6D919B25-B8FE-2544-BF4A-57C7D2E82624}" name="2g-no-hash" dataDxfId="51"/>
     <tableColumn id="8" xr3:uid="{1F6EC33F-9E07-9946-B520-CDAF7F096865}" name="3g-no-hash" dataDxfId="50"/>
     <tableColumn id="9" xr3:uid="{599FF272-DD8C-524E-A507-7C2E8B413884}" name="4g-no-hash" dataDxfId="49"/>
@@ -10868,7 +10873,7 @@
     <tableColumn id="17" xr3:uid="{1DE3F9F6-49FE-E745-B980-F71EBCA09E63}" name="xsk3g-hash-at-both" dataDxfId="41"/>
     <tableColumn id="18" xr3:uid="{AD278835-2793-7B43-A293-DFE7C251B4BB}" name="xsk4g-hash-at-both" dataDxfId="40"/>
     <tableColumn id="19" xr3:uid="{5A4E1F64-BE12-884C-8123-919AF261BBFF}" name="max" dataDxfId="39">
-      <calculatedColumnFormula>MAX($G2:$R2)</calculatedColumnFormula>
+      <calculatedColumnFormula>MAX($H2:$S2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -10876,52 +10881,53 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{8E76FDD7-8736-8647-866D-A5E823752812}" name="Table221" displayName="Table221" ref="B22:S28" totalsRowShown="0">
-  <autoFilter ref="B22:S28" xr:uid="{8E76FDD7-8736-8647-866D-A5E823752812}"/>
-  <tableColumns count="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{8E76FDD7-8736-8647-866D-A5E823752812}" name="Table221" displayName="Table221" ref="B22:T28" totalsRowShown="0">
+  <autoFilter ref="B22:T28" xr:uid="{8E76FDD7-8736-8647-866D-A5E823752812}"/>
+  <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{8FCD49D5-1753-F444-917C-2DB16EC7E772}" name="attribute.index"/>
     <tableColumn id="2" xr3:uid="{F04AC2F4-107D-A141-B38F-DAC2E4F34D1F}" name="attribute"/>
     <tableColumn id="3" xr3:uid="{0FFF0EC7-91B9-5349-A453-4A11F32861E7}" name="supplemented"/>
     <tableColumn id="4" xr3:uid="{4F4CE2D4-6EA5-8743-875D-4B39826CE09A}" name="method.index"/>
-    <tableColumn id="5" xr3:uid="{A350A7AC-CAD0-DF4F-B6DE-6B81F706CB9F}" name="metric"/>
+    <tableColumn id="5" xr3:uid="{A350A7AC-CAD0-DF4F-B6DE-6B81F706CB9F}" name="method"/>
+    <tableColumn id="19" xr3:uid="{01330342-F500-F34F-85C1-5C9E319B9FB7}" name="var"/>
     <tableColumn id="6" xr3:uid="{2E4FEEA9-0BEE-6E40-88AA-00103CAC27A3}" name="2g-no-hash" dataDxfId="38">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{160BDA44-F69D-D947-B86E-47D851D37960}" name="3g-no-hash" dataDxfId="37">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{F15B1771-D901-574D-82B8-9AC3840CE29E}" name="4g-no-hash" dataDxfId="36">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{53977FF0-27DA-8A47-A6EF-A6BD72B0EDCB}" name="xsk2g-no-hash" dataDxfId="35">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{A6219C7C-F7C2-014F-AA0B-1EB06E91A7C9}" name="xsk3g-no-hash" dataDxfId="34">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="11" xr3:uid="{EC476079-B8A2-AB49-AA9B-21AB2CB75D47}" name="xsk4g-no-hash" dataDxfId="33">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{67C0BD80-4381-8D48-BB5A-227F3AD5B85D}" name="2g-hash-at-both" dataDxfId="32">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="13" xr3:uid="{51F4FDD8-A65B-F846-82B1-1BBFBE6C2071}" name="3g-hash-at-both" dataDxfId="31">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="14" xr3:uid="{25A3DE42-A03F-1449-8EA9-9C2AEF49C047}" name="4g-hash-at-both" dataDxfId="30">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="15" xr3:uid="{0E9B26A1-9475-514D-9A18-49CB9953C29F}" name="xsk2g-hash-at-both" dataDxfId="29">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{29971F65-188B-3B4D-A422-38E04002774F}" name="xsk3g-hash-at-both" dataDxfId="28">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="17" xr3:uid="{E93940FB-A186-F842-B24D-34547FBB4AE6}" name="xsk4g-hash-at-both" dataDxfId="27">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="18" xr3:uid="{7519F29A-C8B6-0F4F-A86E-EE62F266F1D4}" name="max" dataDxfId="26">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -10969,7 +10975,7 @@
     <tableColumn id="2" xr3:uid="{EEC53F9C-0442-5747-992F-203761E147F3}" name="attribute"/>
     <tableColumn id="3" xr3:uid="{4182FF18-ECC4-0348-A274-5BAD7C30762D}" name="supplemented"/>
     <tableColumn id="4" xr3:uid="{B74ACBF3-4D7D-E940-8071-1EBF75F4E7D4}" name="method.index"/>
-    <tableColumn id="5" xr3:uid="{16AFB1BC-DAEA-7C4B-8CA4-6FD139B24446}" name="metric"/>
+    <tableColumn id="5" xr3:uid="{16AFB1BC-DAEA-7C4B-8CA4-6FD139B24446}" name="method"/>
     <tableColumn id="6" xr3:uid="{A1BA3681-996C-0A4E-862B-ABEC8C34C9C0}" name="2g-no-hash" dataDxfId="12">
       <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
     </tableColumn>
@@ -17667,7 +17673,7 @@
         <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G22" t="s">
         <v>6</v>
@@ -21566,7 +21572,7 @@
         <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G22" t="s">
         <v>6</v>
@@ -24299,7 +24305,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF853B66-0970-3D46-ADC1-EC10223768C8}">
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="8.75" customWidth="1"/>
@@ -24308,7 +24314,7 @@
     <col min="7" max="19" width="7.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="25" customHeight="1">
+    <row r="1" spans="1:20" ht="25" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -24328,46 +24334,49 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>13</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>14</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>15</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>16</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>17</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>22</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>23</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="25" customHeight="1">
+    <row r="2" spans="1:20" ht="25" customHeight="1">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -24386,48 +24395,48 @@
       <c r="F2" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>0.65</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
         <v>0.64</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2" s="1">
         <v>0.71</v>
       </c>
-      <c r="J2" s="1">
+      <c r="K2" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>0.67</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="1">
         <v>0.65</v>
       </c>
-      <c r="M2" s="1">
+      <c r="N2" s="1">
         <v>0.68</v>
       </c>
-      <c r="N2" s="1">
+      <c r="O2" s="1">
         <v>0.64</v>
       </c>
-      <c r="O2" s="1">
+      <c r="P2" s="1">
         <v>0.69</v>
       </c>
-      <c r="P2" s="1">
+      <c r="Q2" s="1">
         <v>0.63</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="R2" s="1">
         <v>0.57999999999999996</v>
       </c>
-      <c r="R2" s="1">
+      <c r="S2" s="1">
         <v>0.63</v>
       </c>
-      <c r="S2" s="1">
-        <f t="shared" ref="S2:S19" si="0">MAX($G2:$R2)</f>
+      <c r="T2" s="1">
+        <f t="shared" ref="T2:T19" si="0">MAX($H2:$S2)</f>
         <v>0.71</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="25" customHeight="1">
+    <row r="3" spans="1:20" ht="25" customHeight="1">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -24446,48 +24455,48 @@
       <c r="F3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="1">
-        <v>0.72</v>
-      </c>
       <c r="H3" s="1">
         <v>0.72</v>
       </c>
       <c r="I3" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="J3" s="1">
         <v>0.8</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K3" s="1">
         <v>0.62</v>
-      </c>
-      <c r="K3" s="1">
-        <v>0.7</v>
       </c>
       <c r="L3" s="1">
         <v>0.7</v>
       </c>
       <c r="M3" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="N3" s="1">
         <v>0.72</v>
       </c>
-      <c r="N3" s="1">
+      <c r="O3" s="1">
         <v>0.65</v>
       </c>
-      <c r="O3" s="1">
+      <c r="P3" s="1">
         <v>0.73</v>
       </c>
-      <c r="P3" s="1">
+      <c r="Q3" s="1">
         <v>0.68</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="R3" s="1">
         <v>0.64</v>
       </c>
-      <c r="R3" s="1">
+      <c r="S3" s="1">
         <v>0.66</v>
       </c>
-      <c r="S3" s="1">
+      <c r="T3" s="1">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="25" customHeight="1">
+    <row r="4" spans="1:20" ht="25" customHeight="1">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -24506,48 +24515,48 @@
       <c r="F4" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <v>0.67</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>0.66</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
         <v>0.73</v>
       </c>
-      <c r="J4" s="1">
+      <c r="K4" s="1">
         <v>0.61</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>0.66</v>
       </c>
-      <c r="L4" s="1">
+      <c r="M4" s="1">
         <v>0.65</v>
       </c>
-      <c r="M4" s="1">
+      <c r="N4" s="1">
         <v>0.66</v>
       </c>
-      <c r="N4" s="1">
+      <c r="O4" s="1">
         <v>0.56999999999999995</v>
       </c>
-      <c r="O4" s="1">
+      <c r="P4" s="1">
         <v>0.64</v>
       </c>
-      <c r="P4" s="1">
+      <c r="Q4" s="1">
         <v>0.69</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="R4" s="1">
         <v>0.68</v>
       </c>
-      <c r="R4" s="1">
+      <c r="S4" s="1">
         <v>0.6</v>
       </c>
-      <c r="S4" s="1">
+      <c r="T4" s="1">
         <f t="shared" si="0"/>
         <v>0.73</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="25" customHeight="1">
+    <row r="5" spans="1:20" ht="25" customHeight="1">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -24566,48 +24575,48 @@
       <c r="F5" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="1">
-        <v>0.66</v>
-      </c>
       <c r="H5" s="1">
         <v>0.66</v>
       </c>
       <c r="I5" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J5" s="1">
         <v>0.78</v>
       </c>
-      <c r="J5" s="1">
+      <c r="K5" s="1">
         <v>0.59</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>0.69</v>
       </c>
-      <c r="L5" s="1">
+      <c r="M5" s="1">
         <v>0.68</v>
-      </c>
-      <c r="M5" s="1">
-        <v>0.65</v>
       </c>
       <c r="N5" s="1">
         <v>0.65</v>
       </c>
       <c r="O5" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="P5" s="1">
         <v>0.68</v>
       </c>
-      <c r="P5" s="1">
+      <c r="Q5" s="1">
         <v>0.6</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="R5" s="1">
         <v>0.63</v>
       </c>
-      <c r="R5" s="1">
+      <c r="S5" s="1">
         <v>0.65</v>
       </c>
-      <c r="S5" s="1">
+      <c r="T5" s="1">
         <f t="shared" si="0"/>
         <v>0.78</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="25" customHeight="1">
+    <row r="6" spans="1:20" ht="25" customHeight="1">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -24626,48 +24635,48 @@
       <c r="F6" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>0.66</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>0.69</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>0.79</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>0.6</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>0.69</v>
       </c>
-      <c r="L6" s="1">
+      <c r="M6" s="1">
         <v>0.71</v>
       </c>
-      <c r="M6" s="1">
+      <c r="N6" s="1">
         <v>0.69</v>
       </c>
-      <c r="N6" s="1">
+      <c r="O6" s="1">
         <v>0.63</v>
       </c>
-      <c r="O6" s="1">
+      <c r="P6" s="1">
         <v>0.69</v>
       </c>
-      <c r="P6" s="1">
+      <c r="Q6" s="1">
         <v>0.66</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="R6" s="1">
         <v>0.65</v>
       </c>
-      <c r="R6" s="1">
+      <c r="S6" s="1">
         <v>0.67</v>
       </c>
-      <c r="S6" s="1">
+      <c r="T6" s="1">
         <f t="shared" si="0"/>
         <v>0.79</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="25" customHeight="1">
+    <row r="7" spans="1:20" ht="25" customHeight="1">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -24686,48 +24695,48 @@
       <c r="F7" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>0.59</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>0.65</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>0.7</v>
       </c>
-      <c r="J7" s="1">
+      <c r="K7" s="1">
         <v>0.59</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>0.62</v>
       </c>
-      <c r="L7" s="1">
+      <c r="M7" s="1">
         <v>0.67</v>
       </c>
-      <c r="M7" s="1">
+      <c r="N7" s="1">
         <v>0.6</v>
       </c>
-      <c r="N7" s="1">
+      <c r="O7" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="O7" s="1">
+      <c r="P7" s="1">
         <v>0.59</v>
       </c>
-      <c r="P7" s="1">
+      <c r="Q7" s="1">
         <v>0.65</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="R7" s="1">
         <v>0.63</v>
       </c>
-      <c r="R7" s="1">
+      <c r="S7" s="1">
         <v>0.59</v>
       </c>
-      <c r="S7" s="1">
+      <c r="T7" s="1">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="25" customHeight="1">
+    <row r="8" spans="1:20" ht="25" customHeight="1">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -24746,48 +24755,48 @@
       <c r="F8" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>0.75</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>0.73</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>0.78</v>
       </c>
-      <c r="J8" s="1">
+      <c r="K8" s="1">
         <v>0.67</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0.71</v>
       </c>
       <c r="L8" s="1">
         <v>0.71</v>
       </c>
       <c r="M8" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="N8" s="1">
         <v>0.78</v>
       </c>
-      <c r="N8" s="1">
+      <c r="O8" s="1">
         <v>0.7</v>
       </c>
-      <c r="O8" s="1">
+      <c r="P8" s="1">
         <v>0.73</v>
       </c>
-      <c r="P8" s="1">
+      <c r="Q8" s="1">
         <v>0.64</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="R8" s="1">
         <v>0.72</v>
       </c>
-      <c r="R8" s="1">
+      <c r="S8" s="1">
         <v>0.71</v>
       </c>
-      <c r="S8" s="1">
+      <c r="T8" s="1">
         <f t="shared" si="0"/>
         <v>0.78</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="25" customHeight="1">
+    <row r="9" spans="1:20" ht="25" customHeight="1">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -24806,48 +24815,48 @@
       <c r="F9" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>0.77</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>0.69</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>0.79</v>
       </c>
-      <c r="J9" s="1">
+      <c r="K9" s="1">
         <v>0.77</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>0.74</v>
       </c>
-      <c r="L9" s="1">
+      <c r="M9" s="1">
         <v>0.7</v>
       </c>
-      <c r="M9" s="1">
+      <c r="N9" s="1">
         <v>0.82</v>
       </c>
-      <c r="N9" s="1">
+      <c r="O9" s="1">
         <v>0.79</v>
       </c>
-      <c r="O9" s="1">
+      <c r="P9" s="1">
         <v>0.8</v>
       </c>
-      <c r="P9" s="1">
+      <c r="Q9" s="1">
         <v>0.78</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="R9" s="1">
         <v>0.77</v>
       </c>
-      <c r="R9" s="1">
+      <c r="S9" s="1">
         <v>0.71</v>
       </c>
-      <c r="S9" s="1">
+      <c r="T9" s="1">
         <f t="shared" si="0"/>
         <v>0.82</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="25" customHeight="1">
+    <row r="10" spans="1:20" ht="25" customHeight="1">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -24866,48 +24875,48 @@
       <c r="F10" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>0.76</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <v>0.72</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>0.78</v>
       </c>
-      <c r="J10" s="1">
+      <c r="K10" s="1">
         <v>0.7</v>
       </c>
-      <c r="K10" s="1">
+      <c r="L10" s="1">
         <v>0.74</v>
       </c>
-      <c r="L10" s="1">
+      <c r="M10" s="1">
         <v>0.73</v>
       </c>
-      <c r="M10" s="1">
+      <c r="N10" s="1">
         <v>0.83</v>
       </c>
-      <c r="N10" s="1">
+      <c r="O10" s="1">
         <v>0.77</v>
       </c>
-      <c r="O10" s="1">
+      <c r="P10" s="1">
         <v>0.72</v>
       </c>
-      <c r="P10" s="1">
+      <c r="Q10" s="1">
         <v>0.67</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="R10" s="1">
         <v>0.75</v>
       </c>
-      <c r="R10" s="1">
+      <c r="S10" s="1">
         <v>0.72</v>
       </c>
-      <c r="S10" s="1">
+      <c r="T10" s="1">
         <f t="shared" si="0"/>
         <v>0.83</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="25" customHeight="1">
+    <row r="11" spans="1:20" ht="25" customHeight="1">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -24926,48 +24935,48 @@
       <c r="F11" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>0.68</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>0.63</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11" s="1">
         <v>0.74</v>
       </c>
-      <c r="J11" s="1">
+      <c r="K11" s="1">
         <v>0.69</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>0.68</v>
-      </c>
-      <c r="L11" s="1">
-        <v>0.73</v>
       </c>
       <c r="M11" s="1">
         <v>0.73</v>
       </c>
       <c r="N11" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="O11" s="1">
         <v>0.75</v>
       </c>
-      <c r="O11" s="1">
+      <c r="P11" s="1">
         <v>0.71</v>
       </c>
-      <c r="P11" s="1">
+      <c r="Q11" s="1">
         <v>0.66</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="R11" s="1">
         <v>0.69</v>
       </c>
-      <c r="R11" s="1">
+      <c r="S11" s="1">
         <v>0.63</v>
       </c>
-      <c r="S11" s="1">
+      <c r="T11" s="1">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="25" customHeight="1">
+    <row r="12" spans="1:20" ht="25" customHeight="1">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -24986,48 +24995,48 @@
       <c r="F12" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <v>0.68</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
         <v>0.69</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12" s="1">
         <v>0.76</v>
-      </c>
-      <c r="J12" s="1">
-        <v>0.74</v>
       </c>
       <c r="K12" s="1">
         <v>0.74</v>
       </c>
       <c r="L12" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="M12" s="1">
         <v>0.72</v>
       </c>
-      <c r="M12" s="1">
+      <c r="N12" s="1">
         <v>0.76</v>
       </c>
-      <c r="N12" s="1">
+      <c r="O12" s="1">
         <v>0.77</v>
       </c>
-      <c r="O12" s="1">
+      <c r="P12" s="1">
         <v>0.76</v>
       </c>
-      <c r="P12" s="1">
+      <c r="Q12" s="1">
         <v>0.74</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="R12" s="1">
         <v>0.76</v>
       </c>
-      <c r="R12" s="1">
+      <c r="S12" s="1">
         <v>0.7</v>
       </c>
-      <c r="S12" s="1">
+      <c r="T12" s="1">
         <f t="shared" si="0"/>
         <v>0.77</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="25" customHeight="1">
+    <row r="13" spans="1:20" ht="25" customHeight="1">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -25046,48 +25055,48 @@
       <c r="F13" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <v>0.69</v>
       </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
         <v>0.66</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13" s="1">
         <v>0.72</v>
       </c>
-      <c r="J13" s="1">
+      <c r="K13" s="1">
         <v>0.68</v>
       </c>
-      <c r="K13" s="1">
+      <c r="L13" s="1">
         <v>0.72</v>
-      </c>
-      <c r="L13" s="1">
-        <v>0.74</v>
       </c>
       <c r="M13" s="1">
         <v>0.74</v>
       </c>
       <c r="N13" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="O13" s="1">
         <v>0.75</v>
       </c>
-      <c r="O13" s="1">
+      <c r="P13" s="1">
         <v>0.72</v>
       </c>
-      <c r="P13" s="1">
+      <c r="Q13" s="1">
         <v>0.7</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="R13" s="1">
         <v>0.74</v>
       </c>
-      <c r="R13" s="1">
+      <c r="S13" s="1">
         <v>0.68</v>
       </c>
-      <c r="S13" s="1">
+      <c r="T13" s="1">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="25" customHeight="1">
+    <row r="14" spans="1:20" ht="25" customHeight="1">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -25106,11 +25115,8 @@
       <c r="F14" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="1">
-        <v>0.97</v>
-      </c>
       <c r="H14" s="1">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="I14" s="1">
         <v>0.96</v>
@@ -25119,35 +25125,38 @@
         <v>0.96</v>
       </c>
       <c r="K14" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="L14" s="1">
         <v>0.95</v>
       </c>
-      <c r="L14" s="1">
-        <v>0.97</v>
-      </c>
       <c r="M14" s="1">
         <v>0.97</v>
       </c>
       <c r="N14" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="O14" s="1">
         <v>0.99</v>
       </c>
-      <c r="O14" s="1">
-        <v>0.97</v>
-      </c>
       <c r="P14" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="Q14" s="1">
         <v>0.94</v>
       </c>
-      <c r="Q14" s="1">
-        <v>0.97</v>
-      </c>
       <c r="R14" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="S14" s="1">
         <v>0.94</v>
       </c>
-      <c r="S14" s="1">
+      <c r="T14" s="1">
         <f t="shared" si="0"/>
         <v>0.99</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="25" customHeight="1">
+    <row r="15" spans="1:20" ht="25" customHeight="1">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -25166,48 +25175,48 @@
       <c r="F15" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="1">
-        <v>0.97</v>
-      </c>
       <c r="H15" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="I15" s="1">
         <v>0.96</v>
       </c>
-      <c r="I15" s="1">
-        <v>0.97</v>
-      </c>
       <c r="J15" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="K15" s="1">
         <v>0.96</v>
       </c>
-      <c r="K15" s="1">
+      <c r="L15" s="1">
         <v>0.95</v>
       </c>
-      <c r="L15" s="1">
-        <v>0.97</v>
-      </c>
       <c r="M15" s="1">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="N15" s="1">
         <v>0.98</v>
       </c>
       <c r="O15" s="1">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="P15" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="Q15" s="1">
         <v>0.95</v>
       </c>
-      <c r="Q15" s="1">
-        <v>0.97</v>
-      </c>
       <c r="R15" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="S15" s="1">
         <v>0.94</v>
       </c>
-      <c r="S15" s="1">
+      <c r="T15" s="1">
         <f t="shared" si="0"/>
         <v>0.98</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="25" customHeight="1">
+    <row r="16" spans="1:20" ht="25" customHeight="1">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -25226,48 +25235,48 @@
       <c r="F16" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="1">
-        <v>0.97</v>
-      </c>
       <c r="H16" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="I16" s="1">
         <v>0.96</v>
       </c>
-      <c r="I16" s="1">
-        <v>0.97</v>
-      </c>
       <c r="J16" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="K16" s="1">
         <v>0.96</v>
       </c>
-      <c r="K16" s="1">
+      <c r="L16" s="1">
         <v>0.95</v>
       </c>
-      <c r="L16" s="1">
-        <v>0.97</v>
-      </c>
       <c r="M16" s="1">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="N16" s="1">
         <v>0.98</v>
       </c>
       <c r="O16" s="1">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="P16" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="Q16" s="1">
         <v>0.95</v>
       </c>
-      <c r="Q16" s="1">
-        <v>0.97</v>
-      </c>
       <c r="R16" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="S16" s="1">
         <v>0.94</v>
       </c>
-      <c r="S16" s="1">
+      <c r="T16" s="1">
         <f t="shared" si="0"/>
         <v>0.98</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="25" customHeight="1">
+    <row r="17" spans="1:20" ht="25" customHeight="1">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -25286,48 +25295,48 @@
       <c r="F17" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="1">
-        <v>0.97</v>
-      </c>
       <c r="H17" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="I17" s="1">
         <v>0.96</v>
       </c>
-      <c r="I17" s="1">
-        <v>0.97</v>
-      </c>
       <c r="J17" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="K17" s="1">
         <v>0.96</v>
       </c>
-      <c r="K17" s="1">
+      <c r="L17" s="1">
         <v>0.95</v>
       </c>
-      <c r="L17" s="1">
+      <c r="M17" s="1">
         <v>0.96</v>
       </c>
-      <c r="M17" s="1">
-        <v>0.97</v>
-      </c>
       <c r="N17" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="O17" s="1">
         <v>0.98</v>
       </c>
-      <c r="O17" s="1">
+      <c r="P17" s="1">
         <v>0.96</v>
       </c>
-      <c r="P17" s="1">
+      <c r="Q17" s="1">
         <v>0.93</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="R17" s="1">
         <v>0.96</v>
       </c>
-      <c r="R17" s="1">
+      <c r="S17" s="1">
         <v>0.94</v>
       </c>
-      <c r="S17" s="1">
+      <c r="T17" s="1">
         <f t="shared" si="0"/>
         <v>0.98</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="25" customHeight="1">
+    <row r="18" spans="1:20" ht="25" customHeight="1">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -25346,48 +25355,48 @@
       <c r="F18" t="s">
         <v>27</v>
       </c>
-      <c r="G18" s="1">
-        <v>0.97</v>
-      </c>
       <c r="H18" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="I18" s="1">
         <v>0.96</v>
       </c>
-      <c r="I18" s="1">
-        <v>0.97</v>
-      </c>
       <c r="J18" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="K18" s="1">
         <v>0.96</v>
       </c>
-      <c r="K18" s="1">
+      <c r="L18" s="1">
         <v>0.95</v>
       </c>
-      <c r="L18" s="1">
-        <v>0.97</v>
-      </c>
       <c r="M18" s="1">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="N18" s="1">
         <v>0.98</v>
       </c>
       <c r="O18" s="1">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="P18" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="Q18" s="1">
         <v>0.95</v>
       </c>
-      <c r="Q18" s="1">
-        <v>0.97</v>
-      </c>
       <c r="R18" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="S18" s="1">
         <v>0.94</v>
       </c>
-      <c r="S18" s="1">
+      <c r="T18" s="1">
         <f t="shared" si="0"/>
         <v>0.98</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="25" customHeight="1">
+    <row r="19" spans="1:20" ht="25" customHeight="1">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -25406,48 +25415,48 @@
       <c r="F19" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="1">
-        <v>0.97</v>
-      </c>
       <c r="H19" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="I19" s="1">
         <v>0.96</v>
       </c>
-      <c r="I19" s="1">
-        <v>0.97</v>
-      </c>
       <c r="J19" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="K19" s="1">
         <v>0.96</v>
       </c>
-      <c r="K19" s="1">
+      <c r="L19" s="1">
         <v>0.95</v>
       </c>
-      <c r="L19" s="1">
-        <v>0.97</v>
-      </c>
       <c r="M19" s="1">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="N19" s="1">
         <v>0.98</v>
       </c>
       <c r="O19" s="1">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="P19" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="Q19" s="1">
         <v>0.95</v>
       </c>
-      <c r="Q19" s="1">
-        <v>0.97</v>
-      </c>
       <c r="R19" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="S19" s="1">
         <v>0.94</v>
       </c>
-      <c r="S19" s="1">
+      <c r="T19" s="1">
         <f t="shared" si="0"/>
         <v>0.98</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="25" customHeight="1">
+    <row r="22" spans="1:20" ht="25" customHeight="1">
       <c r="B22" t="s">
         <v>1</v>
       </c>
@@ -25461,49 +25470,52 @@
         <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G22" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22" t="s">
         <v>6</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>7</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>8</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>9</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
         <v>10</v>
       </c>
-      <c r="L22" t="s">
+      <c r="M22" t="s">
         <v>11</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>15</v>
       </c>
-      <c r="N22" t="s">
+      <c r="O22" t="s">
         <v>16</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>17</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
         <v>18</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R22" t="s">
         <v>19</v>
       </c>
-      <c r="R22" t="s">
+      <c r="S22" t="s">
         <v>20</v>
       </c>
-      <c r="S22" t="s">
+      <c r="T22" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="25" customHeight="1">
+    <row r="23" spans="1:20" ht="25" customHeight="1">
       <c r="B23">
         <v>1</v>
       </c>
@@ -25518,10 +25530,6 @@
       </c>
       <c r="F23" t="s">
         <v>24</v>
-      </c>
-      <c r="G23" s="1" cm="1">
-        <f t="array" ref="G23">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.72</v>
       </c>
       <c r="H23" s="1" cm="1">
         <f t="array" ref="H23">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
@@ -25529,15 +25537,15 @@
       </c>
       <c r="I23" s="1" cm="1">
         <f t="array" ref="I23">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="J23" s="1" cm="1">
         <f t="array" ref="J23">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.62</v>
+        <v>0.8</v>
       </c>
       <c r="K23" s="1" cm="1">
         <f t="array" ref="K23">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="L23" s="1" cm="1">
         <f t="array" ref="L23">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
@@ -25545,34 +25553,38 @@
       </c>
       <c r="M23" s="1" cm="1">
         <f t="array" ref="M23">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="N23" s="1" cm="1">
         <f t="array" ref="N23">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="O23" s="1" cm="1">
         <f t="array" ref="O23">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
       <c r="P23" s="1" cm="1">
         <f t="array" ref="P23">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.69</v>
+        <v>0.73</v>
       </c>
       <c r="Q23" s="1" cm="1">
         <f t="array" ref="Q23">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.68</v>
+        <v>0.69</v>
       </c>
       <c r="R23" s="1" cm="1">
         <f t="array" ref="R23">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="S23" s="1" cm="1">
         <f t="array" ref="S23">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
+        <v>0.66</v>
+      </c>
+      <c r="T23" s="1" cm="1">
+        <f t="array" ref="T23">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
         <v>0.8</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="25" customHeight="1">
+    <row r="24" spans="1:20" ht="25" customHeight="1">
       <c r="B24">
         <v>1</v>
       </c>
@@ -25588,60 +25600,60 @@
       <c r="F24" t="s">
         <v>24</v>
       </c>
-      <c r="G24" s="1" cm="1">
-        <f t="array" ref="G24">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.66</v>
-      </c>
       <c r="H24" s="1" cm="1">
         <f t="array" ref="H24">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.69</v>
+        <v>0.66</v>
       </c>
       <c r="I24" s="1" cm="1">
         <f t="array" ref="I24">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.79</v>
+        <v>0.69</v>
       </c>
       <c r="J24" s="1" cm="1">
         <f t="array" ref="J24">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.6</v>
+        <v>0.79</v>
       </c>
       <c r="K24" s="1" cm="1">
         <f t="array" ref="K24">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.69</v>
+        <v>0.6</v>
       </c>
       <c r="L24" s="1" cm="1">
         <f t="array" ref="L24">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.71</v>
+        <v>0.69</v>
       </c>
       <c r="M24" s="1" cm="1">
         <f t="array" ref="M24">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.69</v>
+        <v>0.71</v>
       </c>
       <c r="N24" s="1" cm="1">
         <f t="array" ref="N24">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.65</v>
+        <v>0.69</v>
       </c>
       <c r="O24" s="1" cm="1">
         <f t="array" ref="O24">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.69</v>
+        <v>0.65</v>
       </c>
       <c r="P24" s="1" cm="1">
         <f t="array" ref="P24">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.66</v>
+        <v>0.69</v>
       </c>
       <c r="Q24" s="1" cm="1">
         <f t="array" ref="Q24">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="R24" s="1" cm="1">
         <f t="array" ref="R24">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="S24" s="1" cm="1">
         <f t="array" ref="S24">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
+        <v>0.67</v>
+      </c>
+      <c r="T24" s="1" cm="1">
+        <f t="array" ref="T24">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
         <v>0.79</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="25" customHeight="1">
+    <row r="25" spans="1:20" ht="25" customHeight="1">
       <c r="B25">
         <v>2</v>
       </c>
@@ -25657,60 +25669,60 @@
       <c r="F25" t="s">
         <v>24</v>
       </c>
-      <c r="G25" s="1" cm="1">
-        <f t="array" ref="G25">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.77</v>
-      </c>
       <c r="H25" s="1" cm="1">
         <f t="array" ref="H25">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="I25" s="1" cm="1">
         <f t="array" ref="I25">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="J25" s="1" cm="1">
         <f t="array" ref="J25">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="K25" s="1" cm="1">
         <f t="array" ref="K25">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="L25" s="1" cm="1">
         <f t="array" ref="L25">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="M25" s="1" cm="1">
         <f t="array" ref="M25">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="N25" s="1" cm="1">
         <f t="array" ref="N25">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="O25" s="1" cm="1">
         <f t="array" ref="O25">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="P25" s="1" cm="1">
         <f t="array" ref="P25">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="Q25" s="1" cm="1">
         <f t="array" ref="Q25">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="R25" s="1" cm="1">
         <f t="array" ref="R25">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="S25" s="1" cm="1">
         <f t="array" ref="S25">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
+        <v>0.72</v>
+      </c>
+      <c r="T25" s="1" cm="1">
+        <f t="array" ref="T25">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
         <v>0.83</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="25" customHeight="1">
+    <row r="26" spans="1:20" ht="25" customHeight="1">
       <c r="B26">
         <v>2</v>
       </c>
@@ -25725,10 +25737,6 @@
       </c>
       <c r="F26" t="s">
         <v>24</v>
-      </c>
-      <c r="G26" s="1" cm="1">
-        <f t="array" ref="G26">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.69</v>
       </c>
       <c r="H26" s="1" cm="1">
         <f t="array" ref="H26">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
@@ -25736,11 +25744,11 @@
       </c>
       <c r="I26" s="1" cm="1">
         <f t="array" ref="I26">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.76</v>
+        <v>0.69</v>
       </c>
       <c r="J26" s="1" cm="1">
         <f t="array" ref="J26">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="K26" s="1" cm="1">
         <f t="array" ref="K26">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
@@ -25752,34 +25760,38 @@
       </c>
       <c r="M26" s="1" cm="1">
         <f t="array" ref="M26">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="N26" s="1" cm="1">
         <f t="array" ref="N26">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="O26" s="1" cm="1">
         <f t="array" ref="O26">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="P26" s="1" cm="1">
         <f t="array" ref="P26">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="Q26" s="1" cm="1">
         <f t="array" ref="Q26">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="R26" s="1" cm="1">
         <f t="array" ref="R26">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="S26" s="1" cm="1">
         <f t="array" ref="S26">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
+        <v>0.7</v>
+      </c>
+      <c r="T26" s="1" cm="1">
+        <f t="array" ref="T26">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
         <v>0.77</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="25" customHeight="1">
+    <row r="27" spans="1:20" ht="25" customHeight="1">
       <c r="B27">
         <v>3</v>
       </c>
@@ -25795,60 +25807,60 @@
       <c r="F27" t="s">
         <v>24</v>
       </c>
-      <c r="G27" s="1" cm="1">
-        <f t="array" ref="G27">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.97</v>
-      </c>
       <c r="H27" s="1" cm="1">
         <f t="array" ref="H27">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="I27" s="1" cm="1">
         <f t="array" ref="I27">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="J27" s="1" cm="1">
         <f t="array" ref="J27">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="K27" s="1" cm="1">
         <f t="array" ref="K27">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="L27" s="1" cm="1">
         <f t="array" ref="L27">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="M27" s="1" cm="1">
         <f t="array" ref="M27">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="N27" s="1" cm="1">
         <f t="array" ref="N27">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="O27" s="1" cm="1">
         <f t="array" ref="O27">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="P27" s="1" cm="1">
         <f t="array" ref="P27">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="Q27" s="1" cm="1">
         <f t="array" ref="Q27">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="R27" s="1" cm="1">
         <f t="array" ref="R27">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.94</v>
+        <v>0.97</v>
       </c>
       <c r="S27" s="1" cm="1">
         <f t="array" ref="S27">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
+        <v>0.94</v>
+      </c>
+      <c r="T27" s="1" cm="1">
+        <f t="array" ref="T27">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
         <v>0.99</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="25" customHeight="1">
+    <row r="28" spans="1:20" ht="25" customHeight="1">
       <c r="B28">
         <v>3</v>
       </c>
@@ -25864,33 +25876,29 @@
       <c r="F28" t="s">
         <v>24</v>
       </c>
-      <c r="G28" s="1" cm="1">
-        <f t="array" ref="G28">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.97</v>
-      </c>
       <c r="H28" s="1" cm="1">
         <f t="array" ref="H28">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="I28" s="1" cm="1">
         <f t="array" ref="I28">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="J28" s="1" cm="1">
         <f t="array" ref="J28">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="K28" s="1" cm="1">
         <f t="array" ref="K28">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="L28" s="1" cm="1">
         <f t="array" ref="L28">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="M28" s="1" cm="1">
         <f t="array" ref="M28">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="N28" s="1" cm="1">
         <f t="array" ref="N28">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
@@ -25898,27 +25906,31 @@
       </c>
       <c r="O28" s="1" cm="1">
         <f t="array" ref="O28">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="P28" s="1" cm="1">
         <f t="array" ref="P28">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="Q28" s="1" cm="1">
         <f t="array" ref="Q28">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="R28" s="1" cm="1">
         <f t="array" ref="R28">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.94</v>
+        <v>0.97</v>
       </c>
       <c r="S28" s="1" cm="1">
         <f t="array" ref="S28">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
+        <v>0.94</v>
+      </c>
+      <c r="T28" s="1" cm="1">
+        <f t="array" ref="T28">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
         <v>0.98</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:S19">
+  <conditionalFormatting sqref="H2:T19">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -25930,7 +25942,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23:S28">
+  <conditionalFormatting sqref="H23:T28">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -27114,7 +27126,7 @@
         <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G22" t="s">
         <v>6</v>
@@ -28765,7 +28777,7 @@
         <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G22" t="s">
         <v>6</v>
@@ -29256,7 +29268,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{836A2AA9-1EF0-5D45-948B-D5BC48BD61D3}">
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.125" customWidth="1"/>
@@ -29267,7 +29279,7 @@
     <col min="7" max="19" width="9.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="25" customHeight="1">
+    <row r="1" spans="1:20" ht="25" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -29287,46 +29299,49 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>13</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>14</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>15</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>16</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>17</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>22</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>23</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="25" customHeight="1">
+    <row r="2" spans="1:20" ht="25" customHeight="1">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -29345,48 +29360,48 @@
       <c r="F2" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>0.69</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
         <v>0.7</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2" s="1">
         <v>0.65</v>
       </c>
-      <c r="J2" s="1">
+      <c r="K2" s="1">
         <v>0.57999999999999996</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>0.59</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="1">
         <v>0.7</v>
       </c>
-      <c r="M2" s="1">
+      <c r="N2" s="1">
         <v>0.67</v>
       </c>
-      <c r="N2" s="1">
+      <c r="O2" s="1">
         <v>0.74</v>
       </c>
-      <c r="O2" s="1">
+      <c r="P2" s="1">
         <v>0.68</v>
       </c>
-      <c r="P2" s="1">
+      <c r="Q2" s="1">
         <v>0.62</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="R2" s="1">
         <v>0.57999999999999996</v>
       </c>
-      <c r="R2" s="1">
+      <c r="S2" s="1">
         <v>0.7</v>
       </c>
-      <c r="S2" s="1">
-        <f t="shared" ref="S2:S19" si="0">MAX($G2:$R2)</f>
+      <c r="T2" s="1">
+        <f t="shared" ref="T2:T19" si="0">MAX($H2:$S2)</f>
         <v>0.74</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="25" customHeight="1">
+    <row r="3" spans="1:20" ht="25" customHeight="1">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -29405,48 +29420,48 @@
       <c r="F3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1">
         <v>0.65</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <v>0.69</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>0.66</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K3" s="1">
         <v>0.63</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>0.65</v>
       </c>
-      <c r="L3" s="1">
+      <c r="M3" s="1">
         <v>0.66</v>
       </c>
-      <c r="M3" s="1">
+      <c r="N3" s="1">
         <v>0.72</v>
       </c>
-      <c r="N3" s="1">
+      <c r="O3" s="1">
         <v>0.75</v>
       </c>
-      <c r="O3" s="1">
+      <c r="P3" s="1">
         <v>0.71</v>
       </c>
-      <c r="P3" s="1">
+      <c r="Q3" s="1">
         <v>0.64</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="R3" s="1">
         <v>0.63</v>
       </c>
-      <c r="R3" s="1">
+      <c r="S3" s="1">
         <v>0.68</v>
       </c>
-      <c r="S3" s="1">
+      <c r="T3" s="1">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="25" customHeight="1">
+    <row r="4" spans="1:20" ht="25" customHeight="1">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -29465,48 +29480,48 @@
       <c r="F4" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="1">
-        <v>0.59</v>
-      </c>
       <c r="H4" s="1">
         <v>0.59</v>
       </c>
       <c r="I4" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="J4" s="1">
         <v>0.61</v>
       </c>
-      <c r="J4" s="1">
+      <c r="K4" s="1">
         <v>0.7</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>0.54</v>
       </c>
-      <c r="L4" s="1">
+      <c r="M4" s="1">
         <v>0.61</v>
       </c>
-      <c r="M4" s="1">
+      <c r="N4" s="1">
         <v>0.7</v>
       </c>
-      <c r="N4" s="1">
+      <c r="O4" s="1">
         <v>0.68</v>
       </c>
-      <c r="O4" s="1">
+      <c r="P4" s="1">
         <v>0.71</v>
       </c>
-      <c r="P4" s="1">
+      <c r="Q4" s="1">
         <v>0.56000000000000005</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="R4" s="1">
         <v>0.59</v>
       </c>
-      <c r="R4" s="1">
+      <c r="S4" s="1">
         <v>0.61</v>
       </c>
-      <c r="S4" s="1">
+      <c r="T4" s="1">
         <f t="shared" si="0"/>
         <v>0.71</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="25" customHeight="1">
+    <row r="5" spans="1:20" ht="25" customHeight="1">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -29525,48 +29540,48 @@
       <c r="F5" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>0.63</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>0.61</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <v>0.66</v>
       </c>
-      <c r="J5" s="1">
+      <c r="K5" s="1">
         <v>0.61</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>0.57999999999999996</v>
       </c>
-      <c r="L5" s="1">
+      <c r="M5" s="1">
         <v>0.63</v>
       </c>
-      <c r="M5" s="1">
+      <c r="N5" s="1">
         <v>0.6</v>
       </c>
-      <c r="N5" s="1">
+      <c r="O5" s="1">
         <v>0.72</v>
       </c>
-      <c r="O5" s="1">
+      <c r="P5" s="1">
         <v>0.64</v>
       </c>
-      <c r="P5" s="1">
+      <c r="Q5" s="1">
         <v>0.6</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="R5" s="1">
         <v>0.59</v>
       </c>
-      <c r="R5" s="1">
+      <c r="S5" s="1">
         <v>0.65</v>
       </c>
-      <c r="S5" s="1">
+      <c r="T5" s="1">
         <f t="shared" si="0"/>
         <v>0.72</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="25" customHeight="1">
+    <row r="6" spans="1:20" ht="25" customHeight="1">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -29585,48 +29600,48 @@
       <c r="F6" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>0.63</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>0.66</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0.63</v>
       </c>
       <c r="J6" s="1">
         <v>0.63</v>
       </c>
       <c r="K6" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="L6" s="1">
         <v>0.65</v>
       </c>
-      <c r="L6" s="1">
+      <c r="M6" s="1">
         <v>0.66</v>
       </c>
-      <c r="M6" s="1">
+      <c r="N6" s="1">
         <v>0.67</v>
-      </c>
-      <c r="N6" s="1">
-        <v>0.71</v>
       </c>
       <c r="O6" s="1">
         <v>0.71</v>
       </c>
       <c r="P6" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="Q6" s="1">
         <v>0.65</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="R6" s="1">
         <v>0.63</v>
       </c>
-      <c r="R6" s="1">
+      <c r="S6" s="1">
         <v>0.68</v>
       </c>
-      <c r="S6" s="1">
+      <c r="T6" s="1">
         <f t="shared" si="0"/>
         <v>0.71</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="25" customHeight="1">
+    <row r="7" spans="1:20" ht="25" customHeight="1">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -29645,48 +29660,48 @@
       <c r="F7" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>0.47</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>0.57999999999999996</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0.63</v>
       </c>
       <c r="J7" s="1">
         <v>0.63</v>
       </c>
       <c r="K7" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="L7" s="1">
         <v>0.56000000000000005</v>
       </c>
-      <c r="L7" s="1">
+      <c r="M7" s="1">
         <v>0.59</v>
       </c>
-      <c r="M7" s="1">
+      <c r="N7" s="1">
         <v>0.67</v>
       </c>
-      <c r="N7" s="1">
+      <c r="O7" s="1">
         <v>0.62</v>
       </c>
-      <c r="O7" s="1">
+      <c r="P7" s="1">
         <v>0.7</v>
       </c>
-      <c r="P7" s="1">
+      <c r="Q7" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="R7" s="1">
         <v>0.51</v>
       </c>
-      <c r="R7" s="1">
+      <c r="S7" s="1">
         <v>0.59</v>
       </c>
-      <c r="S7" s="1">
+      <c r="T7" s="1">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="25" customHeight="1">
+    <row r="8" spans="1:20" ht="25" customHeight="1">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -29705,48 +29720,48 @@
       <c r="F8" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>0.82</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>0.67</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0.68</v>
       </c>
       <c r="J8" s="1">
         <v>0.68</v>
       </c>
       <c r="K8" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="L8" s="1">
         <v>0.57999999999999996</v>
       </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
         <v>0.59</v>
       </c>
-      <c r="M8" s="1">
+      <c r="N8" s="1">
         <v>0.79</v>
-      </c>
-      <c r="N8" s="1">
-        <v>0.75</v>
       </c>
       <c r="O8" s="1">
         <v>0.75</v>
       </c>
       <c r="P8" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="Q8" s="1">
         <v>0.69</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="R8" s="1">
         <v>0.56000000000000005</v>
       </c>
-      <c r="R8" s="1">
+      <c r="S8" s="1">
         <v>0.68</v>
       </c>
-      <c r="S8" s="1">
+      <c r="T8" s="1">
         <f t="shared" si="0"/>
         <v>0.82</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="25" customHeight="1">
+    <row r="9" spans="1:20" ht="25" customHeight="1">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -29765,48 +29780,48 @@
       <c r="F9" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>0.76</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>0.77</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>0.74</v>
       </c>
-      <c r="J9" s="1">
+      <c r="K9" s="1">
         <v>0.78</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>0.68</v>
       </c>
-      <c r="L9" s="1">
+      <c r="M9" s="1">
         <v>0.7</v>
       </c>
-      <c r="M9" s="1">
+      <c r="N9" s="1">
         <v>0.75</v>
       </c>
-      <c r="N9" s="1">
+      <c r="O9" s="1">
         <v>0.73</v>
-      </c>
-      <c r="O9" s="1">
-        <v>0.75</v>
       </c>
       <c r="P9" s="1">
         <v>0.75</v>
       </c>
       <c r="Q9" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="R9" s="1">
         <v>0.68</v>
       </c>
-      <c r="R9" s="1">
+      <c r="S9" s="1">
         <v>0.7</v>
       </c>
-      <c r="S9" s="1">
+      <c r="T9" s="1">
         <f t="shared" si="0"/>
         <v>0.78</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="25" customHeight="1">
+    <row r="10" spans="1:20" ht="25" customHeight="1">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -29825,48 +29840,48 @@
       <c r="F10" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>0.75</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <v>0.7</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>0.68</v>
       </c>
-      <c r="J10" s="1">
+      <c r="K10" s="1">
         <v>0.76</v>
       </c>
-      <c r="K10" s="1">
+      <c r="L10" s="1">
         <v>0.68</v>
-      </c>
-      <c r="L10" s="1">
-        <v>0.69</v>
       </c>
       <c r="M10" s="1">
         <v>0.69</v>
       </c>
       <c r="N10" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="O10" s="1">
         <v>0.75</v>
       </c>
-      <c r="O10" s="1">
+      <c r="P10" s="1">
         <v>0.77</v>
       </c>
-      <c r="P10" s="1">
+      <c r="Q10" s="1">
         <v>0.68</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="R10" s="1">
         <v>0.61</v>
       </c>
-      <c r="R10" s="1">
+      <c r="S10" s="1">
         <v>0.7</v>
       </c>
-      <c r="S10" s="1">
+      <c r="T10" s="1">
         <f t="shared" si="0"/>
         <v>0.77</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="25" customHeight="1">
+    <row r="11" spans="1:20" ht="25" customHeight="1">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -29885,48 +29900,48 @@
       <c r="F11" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>0.72</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>0.7</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11" s="1">
         <v>0.69</v>
       </c>
-      <c r="J11" s="1">
+      <c r="K11" s="1">
         <v>0.67</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>0.62</v>
       </c>
-      <c r="L11" s="1">
+      <c r="M11" s="1">
         <v>0.61</v>
       </c>
-      <c r="M11" s="1">
+      <c r="N11" s="1">
         <v>0.72</v>
       </c>
-      <c r="N11" s="1">
+      <c r="O11" s="1">
         <v>0.7</v>
-      </c>
-      <c r="O11" s="1">
-        <v>0.71</v>
       </c>
       <c r="P11" s="1">
         <v>0.71</v>
       </c>
       <c r="Q11" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="R11" s="1">
         <v>0.64</v>
       </c>
-      <c r="R11" s="1">
+      <c r="S11" s="1">
         <v>0.7</v>
       </c>
-      <c r="S11" s="1">
+      <c r="T11" s="1">
         <f t="shared" si="0"/>
         <v>0.72</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="25" customHeight="1">
+    <row r="12" spans="1:20" ht="25" customHeight="1">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -29945,48 +29960,48 @@
       <c r="F12" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <v>0.72</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
         <v>0.71</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12" s="1">
         <v>0.73</v>
       </c>
-      <c r="J12" s="1">
+      <c r="K12" s="1">
         <v>0.72</v>
       </c>
-      <c r="K12" s="1">
+      <c r="L12" s="1">
         <v>0.65</v>
       </c>
-      <c r="L12" s="1">
+      <c r="M12" s="1">
         <v>0.71</v>
       </c>
-      <c r="M12" s="1">
+      <c r="N12" s="1">
         <v>0.69</v>
       </c>
-      <c r="N12" s="1">
+      <c r="O12" s="1">
         <v>0.68</v>
       </c>
-      <c r="O12" s="1">
+      <c r="P12" s="1">
         <v>0.69</v>
       </c>
-      <c r="P12" s="1">
+      <c r="Q12" s="1">
         <v>0.74</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="R12" s="1">
         <v>0.64</v>
       </c>
-      <c r="R12" s="1">
+      <c r="S12" s="1">
         <v>0.71</v>
       </c>
-      <c r="S12" s="1">
+      <c r="T12" s="1">
         <f t="shared" si="0"/>
         <v>0.74</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="25" customHeight="1">
+    <row r="13" spans="1:20" ht="25" customHeight="1">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -30005,48 +30020,48 @@
       <c r="F13" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <v>0.71</v>
       </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
         <v>0.65</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13" s="1">
         <v>0.66</v>
       </c>
-      <c r="J13" s="1">
+      <c r="K13" s="1">
         <v>0.69</v>
       </c>
-      <c r="K13" s="1">
+      <c r="L13" s="1">
         <v>0.75</v>
       </c>
-      <c r="L13" s="1">
+      <c r="M13" s="1">
         <v>0.7</v>
-      </c>
-      <c r="M13" s="1">
-        <v>0.69</v>
       </c>
       <c r="N13" s="1">
         <v>0.69</v>
       </c>
       <c r="O13" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="P13" s="1">
         <v>0.73</v>
       </c>
-      <c r="P13" s="1">
+      <c r="Q13" s="1">
         <v>0.62</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="R13" s="1">
         <v>0.57999999999999996</v>
       </c>
-      <c r="R13" s="1">
+      <c r="S13" s="1">
         <v>0.68</v>
       </c>
-      <c r="S13" s="1">
+      <c r="T13" s="1">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="25" customHeight="1">
+    <row r="14" spans="1:20" ht="25" customHeight="1">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -30065,48 +30080,48 @@
       <c r="F14" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="1">
+      <c r="H14" s="1">
         <v>0.92</v>
       </c>
-      <c r="H14" s="1">
-        <v>0.97</v>
-      </c>
       <c r="I14" s="1">
         <v>0.97</v>
       </c>
       <c r="J14" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="K14" s="1">
         <v>0.94</v>
       </c>
-      <c r="K14" s="1">
-        <v>0.97</v>
-      </c>
       <c r="L14" s="1">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="M14" s="1">
         <v>0.95</v>
       </c>
       <c r="N14" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="O14" s="1">
         <v>0.93</v>
-      </c>
-      <c r="O14" s="1">
-        <v>0.96</v>
       </c>
       <c r="P14" s="1">
         <v>0.96</v>
       </c>
       <c r="Q14" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="R14" s="1">
         <v>0.93</v>
       </c>
-      <c r="R14" s="1">
-        <v>0.97</v>
-      </c>
       <c r="S14" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="T14" s="1">
         <f t="shared" si="0"/>
         <v>0.97</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="25" customHeight="1">
+    <row r="15" spans="1:20" ht="25" customHeight="1">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -30125,26 +30140,23 @@
       <c r="F15" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="1">
+      <c r="H15" s="1">
         <v>0.91</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0.98</v>
       </c>
       <c r="I15" s="1">
         <v>0.98</v>
       </c>
       <c r="J15" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="K15" s="1">
         <v>0.95</v>
       </c>
-      <c r="K15" s="1">
+      <c r="L15" s="1">
         <v>0.96</v>
       </c>
-      <c r="L15" s="1">
+      <c r="M15" s="1">
         <v>0.95</v>
-      </c>
-      <c r="M15" s="1">
-        <v>0.96</v>
       </c>
       <c r="N15" s="1">
         <v>0.96</v>
@@ -30156,17 +30168,20 @@
         <v>0.96</v>
       </c>
       <c r="Q15" s="1">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="R15" s="1">
         <v>0.97</v>
       </c>
       <c r="S15" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="T15" s="1">
         <f t="shared" si="0"/>
         <v>0.98</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="25" customHeight="1">
+    <row r="16" spans="1:20" ht="25" customHeight="1">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -30185,26 +30200,23 @@
       <c r="F16" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="1">
+      <c r="H16" s="1">
         <v>0.91</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0.98</v>
       </c>
       <c r="I16" s="1">
         <v>0.98</v>
       </c>
       <c r="J16" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="K16" s="1">
         <v>0.95</v>
       </c>
-      <c r="K16" s="1">
+      <c r="L16" s="1">
         <v>0.96</v>
       </c>
-      <c r="L16" s="1">
+      <c r="M16" s="1">
         <v>0.95</v>
-      </c>
-      <c r="M16" s="1">
-        <v>0.96</v>
       </c>
       <c r="N16" s="1">
         <v>0.96</v>
@@ -30216,17 +30228,20 @@
         <v>0.96</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="R16" s="1">
         <v>0.97</v>
       </c>
       <c r="S16" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="T16" s="1">
         <f t="shared" si="0"/>
         <v>0.98</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="25" customHeight="1">
+    <row r="17" spans="1:20" ht="25" customHeight="1">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -30245,48 +30260,48 @@
       <c r="F17" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="1">
+      <c r="H17" s="1">
         <v>0.9</v>
       </c>
-      <c r="H17" s="1">
-        <v>0.97</v>
-      </c>
       <c r="I17" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="J17" s="1">
         <v>0.98</v>
       </c>
-      <c r="J17" s="1">
+      <c r="K17" s="1">
         <v>0.94</v>
-      </c>
-      <c r="K17" s="1">
-        <v>0.95</v>
       </c>
       <c r="L17" s="1">
         <v>0.95</v>
       </c>
       <c r="M17" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="N17" s="1">
         <v>0.91</v>
       </c>
-      <c r="N17" s="1">
+      <c r="O17" s="1">
         <v>0.94</v>
       </c>
-      <c r="O17" s="1">
+      <c r="P17" s="1">
         <v>0.93</v>
-      </c>
-      <c r="P17" s="1">
-        <v>0.96</v>
       </c>
       <c r="Q17" s="1">
         <v>0.96</v>
       </c>
       <c r="R17" s="1">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="S17" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="T17" s="1">
         <f t="shared" si="0"/>
         <v>0.98</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="25" customHeight="1">
+    <row r="18" spans="1:20" ht="25" customHeight="1">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -30305,26 +30320,23 @@
       <c r="F18" t="s">
         <v>27</v>
       </c>
-      <c r="G18" s="1">
+      <c r="H18" s="1">
         <v>0.91</v>
-      </c>
-      <c r="H18" s="1">
-        <v>0.98</v>
       </c>
       <c r="I18" s="1">
         <v>0.98</v>
       </c>
       <c r="J18" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="K18" s="1">
         <v>0.95</v>
       </c>
-      <c r="K18" s="1">
+      <c r="L18" s="1">
         <v>0.96</v>
       </c>
-      <c r="L18" s="1">
+      <c r="M18" s="1">
         <v>0.95</v>
-      </c>
-      <c r="M18" s="1">
-        <v>0.96</v>
       </c>
       <c r="N18" s="1">
         <v>0.96</v>
@@ -30336,17 +30348,20 @@
         <v>0.96</v>
       </c>
       <c r="Q18" s="1">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="R18" s="1">
         <v>0.97</v>
       </c>
       <c r="S18" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="T18" s="1">
         <f t="shared" si="0"/>
         <v>0.98</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="25" customHeight="1">
+    <row r="19" spans="1:20" ht="25" customHeight="1">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -30365,26 +30380,23 @@
       <c r="F19" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <v>0.91</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0.98</v>
       </c>
       <c r="I19" s="1">
         <v>0.98</v>
       </c>
       <c r="J19" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="K19" s="1">
         <v>0.95</v>
       </c>
-      <c r="K19" s="1">
+      <c r="L19" s="1">
         <v>0.96</v>
       </c>
-      <c r="L19" s="1">
+      <c r="M19" s="1">
         <v>0.95</v>
-      </c>
-      <c r="M19" s="1">
-        <v>0.96</v>
       </c>
       <c r="N19" s="1">
         <v>0.96</v>
@@ -30396,17 +30408,20 @@
         <v>0.96</v>
       </c>
       <c r="Q19" s="1">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="R19" s="1">
         <v>0.97</v>
       </c>
       <c r="S19" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="T19" s="1">
         <f t="shared" si="0"/>
         <v>0.98</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="25" customHeight="1">
+    <row r="22" spans="1:20" ht="25" customHeight="1">
       <c r="B22" t="s">
         <v>1</v>
       </c>
@@ -30420,49 +30435,52 @@
         <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G22" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22" t="s">
         <v>6</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>7</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>8</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>12</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
         <v>13</v>
       </c>
-      <c r="L22" t="s">
+      <c r="M22" t="s">
         <v>14</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>15</v>
       </c>
-      <c r="N22" t="s">
+      <c r="O22" t="s">
         <v>16</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>17</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
         <v>21</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R22" t="s">
         <v>22</v>
       </c>
-      <c r="R22" t="s">
+      <c r="S22" t="s">
         <v>23</v>
       </c>
-      <c r="S22" t="s">
+      <c r="T22" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="25" customHeight="1">
+    <row r="23" spans="1:20" ht="25" customHeight="1">
       <c r="B23">
         <v>1</v>
       </c>
@@ -30478,60 +30496,60 @@
       <c r="F23" t="s">
         <v>24</v>
       </c>
-      <c r="G23" s="1" cm="1">
-        <f t="array" ref="G23">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.69</v>
-      </c>
       <c r="H23" s="1" cm="1">
         <f t="array" ref="H23">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.7</v>
+        <v>0.69</v>
       </c>
       <c r="I23" s="1" cm="1">
         <f t="array" ref="I23">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="J23" s="1" cm="1">
         <f t="array" ref="J23">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="K23" s="1" cm="1">
         <f t="array" ref="K23">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="L23" s="1" cm="1">
         <f t="array" ref="L23">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="M23" s="1" cm="1">
         <f t="array" ref="M23">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="N23" s="1" cm="1">
         <f t="array" ref="N23">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="O23" s="1" cm="1">
         <f t="array" ref="O23">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="P23" s="1" cm="1">
         <f t="array" ref="P23">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="Q23" s="1" cm="1">
         <f t="array" ref="Q23">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="R23" s="1" cm="1">
         <f t="array" ref="R23">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="S23" s="1" cm="1">
         <f t="array" ref="S23">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
+        <v>0.7</v>
+      </c>
+      <c r="T23" s="1" cm="1">
+        <f t="array" ref="T23">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
         <v>0.75</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="25" customHeight="1">
+    <row r="24" spans="1:20" ht="25" customHeight="1">
       <c r="B24">
         <v>1</v>
       </c>
@@ -30547,13 +30565,9 @@
       <c r="F24" t="s">
         <v>24</v>
       </c>
-      <c r="G24" s="1" cm="1">
-        <f t="array" ref="G24">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.63</v>
-      </c>
       <c r="H24" s="1" cm="1">
         <f t="array" ref="H24">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="I24" s="1" cm="1">
         <f t="array" ref="I24">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
@@ -30561,46 +30575,50 @@
       </c>
       <c r="J24" s="1" cm="1">
         <f t="array" ref="J24">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="K24" s="1" cm="1">
         <f t="array" ref="K24">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="L24" s="1" cm="1">
         <f t="array" ref="L24">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="M24" s="1" cm="1">
         <f t="array" ref="M24">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="N24" s="1" cm="1">
         <f t="array" ref="N24">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="O24" s="1" cm="1">
         <f t="array" ref="O24">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="P24" s="1" cm="1">
         <f t="array" ref="P24">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="Q24" s="1" cm="1">
         <f t="array" ref="Q24">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="R24" s="1" cm="1">
         <f t="array" ref="R24">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="S24" s="1" cm="1">
         <f t="array" ref="S24">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
+        <v>0.68</v>
+      </c>
+      <c r="T24" s="1" cm="1">
+        <f t="array" ref="T24">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
         <v>0.72</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="25" customHeight="1">
+    <row r="25" spans="1:20" ht="25" customHeight="1">
       <c r="B25">
         <v>2</v>
       </c>
@@ -30616,60 +30634,60 @@
       <c r="F25" t="s">
         <v>24</v>
       </c>
-      <c r="G25" s="1" cm="1">
-        <f t="array" ref="G25">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.82</v>
-      </c>
       <c r="H25" s="1" cm="1">
         <f t="array" ref="H25">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="I25" s="1" cm="1">
         <f t="array" ref="I25">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="J25" s="1" cm="1">
         <f t="array" ref="J25">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="K25" s="1" cm="1">
         <f t="array" ref="K25">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.68</v>
+        <v>0.78</v>
       </c>
       <c r="L25" s="1" cm="1">
         <f t="array" ref="L25">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="M25" s="1" cm="1">
         <f t="array" ref="M25">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.79</v>
+        <v>0.7</v>
       </c>
       <c r="N25" s="1" cm="1">
         <f t="array" ref="N25">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="O25" s="1" cm="1">
         <f t="array" ref="O25">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="P25" s="1" cm="1">
         <f t="array" ref="P25">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="Q25" s="1" cm="1">
         <f t="array" ref="Q25">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="R25" s="1" cm="1">
         <f t="array" ref="R25">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="S25" s="1" cm="1">
         <f t="array" ref="S25">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
+        <v>0.7</v>
+      </c>
+      <c r="T25" s="1" cm="1">
+        <f t="array" ref="T25">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
         <v>0.82</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="25" customHeight="1">
+    <row r="26" spans="1:20" ht="25" customHeight="1">
       <c r="B26">
         <v>2</v>
       </c>
@@ -30685,60 +30703,60 @@
       <c r="F26" t="s">
         <v>24</v>
       </c>
-      <c r="G26" s="1" cm="1">
-        <f t="array" ref="G26">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.72</v>
-      </c>
       <c r="H26" s="1" cm="1">
         <f t="array" ref="H26">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="I26" s="1" cm="1">
         <f t="array" ref="I26">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="J26" s="1" cm="1">
         <f t="array" ref="J26">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="K26" s="1" cm="1">
         <f t="array" ref="K26">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="L26" s="1" cm="1">
         <f t="array" ref="L26">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="M26" s="1" cm="1">
         <f t="array" ref="M26">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="N26" s="1" cm="1">
         <f t="array" ref="N26">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="O26" s="1" cm="1">
         <f t="array" ref="O26">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="P26" s="1" cm="1">
         <f t="array" ref="P26">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="Q26" s="1" cm="1">
         <f t="array" ref="Q26">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="R26" s="1" cm="1">
         <f t="array" ref="R26">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="S26" s="1" cm="1">
         <f t="array" ref="S26">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
+        <v>0.71</v>
+      </c>
+      <c r="T26" s="1" cm="1">
+        <f t="array" ref="T26">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
         <v>0.75</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="25" customHeight="1">
+    <row r="27" spans="1:20" ht="25" customHeight="1">
       <c r="B27">
         <v>3</v>
       </c>
@@ -30754,13 +30772,9 @@
       <c r="F27" t="s">
         <v>24</v>
       </c>
-      <c r="G27" s="1" cm="1">
-        <f t="array" ref="G27">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.92</v>
-      </c>
       <c r="H27" s="1" cm="1">
         <f t="array" ref="H27">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
       <c r="I27" s="1" cm="1">
         <f t="array" ref="I27">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
@@ -30768,19 +30782,19 @@
       </c>
       <c r="J27" s="1" cm="1">
         <f t="array" ref="J27">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="K27" s="1" cm="1">
         <f t="array" ref="K27">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="L27" s="1" cm="1">
         <f t="array" ref="L27">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="M27" s="1" cm="1">
         <f t="array" ref="M27">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="N27" s="1" cm="1">
         <f t="array" ref="N27">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
@@ -30796,7 +30810,7 @@
       </c>
       <c r="Q27" s="1" cm="1">
         <f t="array" ref="Q27">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="R27" s="1" cm="1">
         <f t="array" ref="R27">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
@@ -30804,10 +30818,14 @@
       </c>
       <c r="S27" s="1" cm="1">
         <f t="array" ref="S27">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
+        <v>0.97</v>
+      </c>
+      <c r="T27" s="1" cm="1">
+        <f t="array" ref="T27">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
         <v>0.98</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="25" customHeight="1">
+    <row r="28" spans="1:20" ht="25" customHeight="1">
       <c r="B28">
         <v>3</v>
       </c>
@@ -30823,13 +30841,9 @@
       <c r="F28" t="s">
         <v>24</v>
       </c>
-      <c r="G28" s="1" cm="1">
-        <f t="array" ref="G28">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.91</v>
-      </c>
       <c r="H28" s="1" cm="1">
         <f t="array" ref="H28">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="I28" s="1" cm="1">
         <f t="array" ref="I28">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
@@ -30837,19 +30851,19 @@
       </c>
       <c r="J28" s="1" cm="1">
         <f t="array" ref="J28">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="K28" s="1" cm="1">
         <f t="array" ref="K28">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="L28" s="1" cm="1">
         <f t="array" ref="L28">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="M28" s="1" cm="1">
         <f t="array" ref="M28">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="N28" s="1" cm="1">
         <f t="array" ref="N28">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
@@ -30865,7 +30879,7 @@
       </c>
       <c r="Q28" s="1" cm="1">
         <f t="array" ref="Q28">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="R28" s="1" cm="1">
         <f t="array" ref="R28">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
@@ -30873,11 +30887,15 @@
       </c>
       <c r="S28" s="1" cm="1">
         <f t="array" ref="S28">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
+        <v>0.97</v>
+      </c>
+      <c r="T28" s="1" cm="1">
+        <f t="array" ref="T28">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
         <v>0.98</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:S19">
+  <conditionalFormatting sqref="H2:T19">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -30889,7 +30907,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23:S28">
+  <conditionalFormatting sqref="H23:T28">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -30911,7 +30929,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E47D41D-DB8B-324A-8295-A917B69BC11A}">
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="9.125" customWidth="1"/>
@@ -30920,7 +30938,7 @@
     <col min="7" max="19" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="25" customHeight="1">
+    <row r="1" spans="1:20" ht="25" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -30940,46 +30958,49 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>13</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>14</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>15</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>16</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>17</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>22</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>23</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="25" customHeight="1">
+    <row r="2" spans="1:20" ht="25" customHeight="1">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -30998,48 +31019,48 @@
       <c r="F2" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>0.6</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
         <v>0.65</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.63</v>
       </c>
       <c r="J2" s="1">
         <v>0.63</v>
       </c>
       <c r="K2" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="L2" s="1">
         <v>0.71</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="1">
         <v>0.61</v>
       </c>
-      <c r="M2" s="1">
+      <c r="N2" s="1">
         <v>0.64</v>
       </c>
-      <c r="N2" s="1">
+      <c r="O2" s="1">
         <v>0.65</v>
       </c>
-      <c r="O2" s="1">
+      <c r="P2" s="1">
         <v>0.66</v>
       </c>
-      <c r="P2" s="1">
+      <c r="Q2" s="1">
         <v>0.59</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="R2" s="1">
         <v>0.62</v>
       </c>
-      <c r="R2" s="1">
+      <c r="S2" s="1">
         <v>0.57999999999999996</v>
       </c>
-      <c r="S2" s="1">
-        <f t="shared" ref="S2:S19" si="0">MAX($G2:$R2)</f>
+      <c r="T2" s="1">
+        <f t="shared" ref="T2:T19" si="0">MAX($H2:$S2)</f>
         <v>0.71</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="25" customHeight="1">
+    <row r="3" spans="1:20" ht="25" customHeight="1">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -31058,48 +31079,48 @@
       <c r="F3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1">
         <v>0.72</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <v>0.67</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>0.76</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K3" s="1">
         <v>0.67</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>0.73</v>
       </c>
-      <c r="L3" s="1">
+      <c r="M3" s="1">
         <v>0.62</v>
       </c>
-      <c r="M3" s="1">
+      <c r="N3" s="1">
         <v>0.63</v>
-      </c>
-      <c r="N3" s="1">
-        <v>0.68</v>
       </c>
       <c r="O3" s="1">
         <v>0.68</v>
       </c>
       <c r="P3" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="Q3" s="1">
         <v>0.59</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="R3" s="1">
         <v>0.62</v>
       </c>
-      <c r="R3" s="1">
+      <c r="S3" s="1">
         <v>0.64</v>
       </c>
-      <c r="S3" s="1">
+      <c r="T3" s="1">
         <f t="shared" si="0"/>
         <v>0.76</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="25" customHeight="1">
+    <row r="4" spans="1:20" ht="25" customHeight="1">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -31118,48 +31139,48 @@
       <c r="F4" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <v>0.59</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>0.64</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
         <v>0.66</v>
       </c>
-      <c r="J4" s="1">
+      <c r="K4" s="1">
         <v>0.6</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>0.68</v>
       </c>
-      <c r="L4" s="1">
+      <c r="M4" s="1">
         <v>0.54</v>
       </c>
-      <c r="M4" s="1">
+      <c r="N4" s="1">
         <v>0.71</v>
       </c>
-      <c r="N4" s="1">
+      <c r="O4" s="1">
         <v>0.61</v>
       </c>
-      <c r="O4" s="1">
+      <c r="P4" s="1">
         <v>0.63</v>
       </c>
-      <c r="P4" s="1">
+      <c r="Q4" s="1">
         <v>0.65</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="R4" s="1">
         <v>0.64</v>
       </c>
-      <c r="R4" s="1">
+      <c r="S4" s="1">
         <v>0.66</v>
       </c>
-      <c r="S4" s="1">
+      <c r="T4" s="1">
         <f t="shared" si="0"/>
         <v>0.71</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="25" customHeight="1">
+    <row r="5" spans="1:20" ht="25" customHeight="1">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -31178,48 +31199,48 @@
       <c r="F5" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>0.66</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>0.67</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <v>0.66</v>
       </c>
-      <c r="J5" s="1">
+      <c r="K5" s="1">
         <v>0.63</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>0.69</v>
       </c>
-      <c r="L5" s="1">
+      <c r="M5" s="1">
         <v>0.6</v>
       </c>
-      <c r="M5" s="1">
+      <c r="N5" s="1">
         <v>0.59</v>
       </c>
-      <c r="N5" s="1">
+      <c r="O5" s="1">
         <v>0.69</v>
       </c>
-      <c r="O5" s="1">
+      <c r="P5" s="1">
         <v>0.68</v>
       </c>
-      <c r="P5" s="1">
+      <c r="Q5" s="1">
         <v>0.57999999999999996</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="R5" s="1">
         <v>0.61</v>
       </c>
-      <c r="R5" s="1">
+      <c r="S5" s="1">
         <v>0.59</v>
       </c>
-      <c r="S5" s="1">
+      <c r="T5" s="1">
         <f t="shared" si="0"/>
         <v>0.69</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="25" customHeight="1">
+    <row r="6" spans="1:20" ht="25" customHeight="1">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -31238,48 +31259,48 @@
       <c r="F6" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="1">
-        <v>0.66</v>
-      </c>
       <c r="H6" s="1">
         <v>0.66</v>
       </c>
       <c r="I6" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J6" s="1">
         <v>0.72</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>0.63</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>0.73</v>
       </c>
-      <c r="L6" s="1">
+      <c r="M6" s="1">
         <v>0.61</v>
       </c>
-      <c r="M6" s="1">
+      <c r="N6" s="1">
         <v>0.59</v>
       </c>
-      <c r="N6" s="1">
+      <c r="O6" s="1">
         <v>0.7</v>
       </c>
-      <c r="O6" s="1">
+      <c r="P6" s="1">
         <v>0.68</v>
       </c>
-      <c r="P6" s="1">
+      <c r="Q6" s="1">
         <v>0.63</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="R6" s="1">
         <v>0.61</v>
       </c>
-      <c r="R6" s="1">
+      <c r="S6" s="1">
         <v>0.62</v>
       </c>
-      <c r="S6" s="1">
+      <c r="T6" s="1">
         <f t="shared" si="0"/>
         <v>0.73</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="25" customHeight="1">
+    <row r="7" spans="1:20" ht="25" customHeight="1">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -31298,48 +31319,48 @@
       <c r="F7" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>0.59</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>0.61</v>
       </c>
-      <c r="J7" s="1">
+      <c r="K7" s="1">
         <v>0.63</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>0.71</v>
       </c>
-      <c r="L7" s="1">
+      <c r="M7" s="1">
         <v>0.52</v>
       </c>
-      <c r="M7" s="1">
+      <c r="N7" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="N7" s="1">
+      <c r="O7" s="1">
         <v>0.66</v>
       </c>
-      <c r="O7" s="1">
+      <c r="P7" s="1">
         <v>0.57999999999999996</v>
       </c>
-      <c r="P7" s="1">
+      <c r="Q7" s="1">
         <v>0.61</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="R7" s="1">
         <v>0.62</v>
       </c>
-      <c r="R7" s="1">
+      <c r="S7" s="1">
         <v>0.61</v>
       </c>
-      <c r="S7" s="1">
+      <c r="T7" s="1">
         <f t="shared" si="0"/>
         <v>0.71</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="25" customHeight="1">
+    <row r="8" spans="1:20" ht="25" customHeight="1">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -31358,48 +31379,48 @@
       <c r="F8" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>0.77</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>0.72</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>0.64</v>
       </c>
-      <c r="J8" s="1">
+      <c r="K8" s="1">
         <v>0.71</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>0.77</v>
       </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
         <v>0.71</v>
       </c>
-      <c r="M8" s="1">
+      <c r="N8" s="1">
         <v>0.75</v>
       </c>
-      <c r="N8" s="1">
+      <c r="O8" s="1">
         <v>0.76</v>
       </c>
-      <c r="O8" s="1">
+      <c r="P8" s="1">
         <v>0.77</v>
-      </c>
-      <c r="P8" s="1">
-        <v>0.68</v>
       </c>
       <c r="Q8" s="1">
         <v>0.68</v>
       </c>
       <c r="R8" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="S8" s="1">
         <v>0.77</v>
       </c>
-      <c r="S8" s="1">
+      <c r="T8" s="1">
         <f t="shared" si="0"/>
         <v>0.77</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="25" customHeight="1">
+    <row r="9" spans="1:20" ht="25" customHeight="1">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -31418,48 +31439,48 @@
       <c r="F9" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>0.76</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0.75</v>
       </c>
       <c r="I9" s="1">
         <v>0.75</v>
       </c>
       <c r="J9" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="K9" s="1">
         <v>0.81</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>0.82</v>
       </c>
-      <c r="L9" s="1">
+      <c r="M9" s="1">
         <v>0.72</v>
       </c>
-      <c r="M9" s="1">
+      <c r="N9" s="1">
         <v>0.71</v>
       </c>
-      <c r="N9" s="1">
+      <c r="O9" s="1">
         <v>0.77</v>
       </c>
-      <c r="O9" s="1">
+      <c r="P9" s="1">
         <v>0.81</v>
       </c>
-      <c r="P9" s="1">
+      <c r="Q9" s="1">
         <v>0.73</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="R9" s="1">
         <v>0.72</v>
       </c>
-      <c r="R9" s="1">
+      <c r="S9" s="1">
         <v>0.75</v>
       </c>
-      <c r="S9" s="1">
+      <c r="T9" s="1">
         <f t="shared" si="0"/>
         <v>0.82</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="25" customHeight="1">
+    <row r="10" spans="1:20" ht="25" customHeight="1">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -31478,48 +31499,48 @@
       <c r="F10" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>0.74</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <v>0.73</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>0.75</v>
       </c>
-      <c r="J10" s="1">
+      <c r="K10" s="1">
         <v>0.74</v>
       </c>
-      <c r="K10" s="1">
+      <c r="L10" s="1">
         <v>0.78</v>
       </c>
-      <c r="L10" s="1">
+      <c r="M10" s="1">
         <v>0.72</v>
       </c>
-      <c r="M10" s="1">
+      <c r="N10" s="1">
         <v>0.66</v>
       </c>
-      <c r="N10" s="1">
+      <c r="O10" s="1">
         <v>0.75</v>
       </c>
-      <c r="O10" s="1">
+      <c r="P10" s="1">
         <v>0.71</v>
       </c>
-      <c r="P10" s="1">
+      <c r="Q10" s="1">
         <v>0.67</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>0.74</v>
       </c>
       <c r="R10" s="1">
         <v>0.74</v>
       </c>
       <c r="S10" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="T10" s="1">
         <f t="shared" si="0"/>
         <v>0.78</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="25" customHeight="1">
+    <row r="11" spans="1:20" ht="25" customHeight="1">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -31538,48 +31559,48 @@
       <c r="F11" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>0.71</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>0.67</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11" s="1">
         <v>0.63</v>
       </c>
-      <c r="J11" s="1">
+      <c r="K11" s="1">
         <v>0.73</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>0.79</v>
       </c>
-      <c r="L11" s="1">
+      <c r="M11" s="1">
         <v>0.66</v>
       </c>
-      <c r="M11" s="1">
+      <c r="N11" s="1">
         <v>0.68</v>
       </c>
-      <c r="N11" s="1">
+      <c r="O11" s="1">
         <v>0.79</v>
       </c>
-      <c r="O11" s="1">
+      <c r="P11" s="1">
         <v>0.69</v>
       </c>
-      <c r="P11" s="1">
+      <c r="Q11" s="1">
         <v>0.66</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="R11" s="1">
         <v>0.75</v>
       </c>
-      <c r="R11" s="1">
+      <c r="S11" s="1">
         <v>0.74</v>
       </c>
-      <c r="S11" s="1">
+      <c r="T11" s="1">
         <f t="shared" si="0"/>
         <v>0.79</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="25" customHeight="1">
+    <row r="12" spans="1:20" ht="25" customHeight="1">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -31598,48 +31619,48 @@
       <c r="F12" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <v>0.72</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
         <v>0.76</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12" s="1">
         <v>0.71</v>
       </c>
-      <c r="J12" s="1">
+      <c r="K12" s="1">
         <v>0.77</v>
       </c>
-      <c r="K12" s="1">
+      <c r="L12" s="1">
         <v>0.78</v>
       </c>
-      <c r="L12" s="1">
+      <c r="M12" s="1">
         <v>0.69</v>
       </c>
-      <c r="M12" s="1">
+      <c r="N12" s="1">
         <v>0.68</v>
       </c>
-      <c r="N12" s="1">
+      <c r="O12" s="1">
         <v>0.83</v>
       </c>
-      <c r="O12" s="1">
+      <c r="P12" s="1">
         <v>0.75</v>
       </c>
-      <c r="P12" s="1">
+      <c r="Q12" s="1">
         <v>0.68</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="R12" s="1">
         <v>0.72</v>
       </c>
-      <c r="R12" s="1">
+      <c r="S12" s="1">
         <v>0.77</v>
       </c>
-      <c r="S12" s="1">
+      <c r="T12" s="1">
         <f t="shared" si="0"/>
         <v>0.83</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="25" customHeight="1">
+    <row r="13" spans="1:20" ht="25" customHeight="1">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -31658,48 +31679,48 @@
       <c r="F13" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <v>0.71</v>
       </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
         <v>0.7</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13" s="1">
         <v>0.61</v>
       </c>
-      <c r="J13" s="1">
+      <c r="K13" s="1">
         <v>0.7</v>
       </c>
-      <c r="K13" s="1">
+      <c r="L13" s="1">
         <v>0.72</v>
       </c>
-      <c r="L13" s="1">
+      <c r="M13" s="1">
         <v>0.67</v>
       </c>
-      <c r="M13" s="1">
+      <c r="N13" s="1">
         <v>0.6</v>
       </c>
-      <c r="N13" s="1">
+      <c r="O13" s="1">
         <v>0.74</v>
       </c>
-      <c r="O13" s="1">
+      <c r="P13" s="1">
         <v>0.71</v>
       </c>
-      <c r="P13" s="1">
+      <c r="Q13" s="1">
         <v>0.64</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="R13" s="1">
         <v>0.7</v>
       </c>
-      <c r="R13" s="1">
+      <c r="S13" s="1">
         <v>0.74</v>
       </c>
-      <c r="S13" s="1">
+      <c r="T13" s="1">
         <f t="shared" si="0"/>
         <v>0.74</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="25" customHeight="1">
+    <row r="14" spans="1:20" ht="25" customHeight="1">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -31718,48 +31739,48 @@
       <c r="F14" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="1">
+      <c r="H14" s="1">
         <v>0.98</v>
       </c>
-      <c r="H14" s="1">
-        <v>0.97</v>
-      </c>
       <c r="I14" s="1">
         <v>0.97</v>
       </c>
       <c r="J14" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="K14" s="1">
         <v>0.99</v>
       </c>
-      <c r="K14" s="1">
+      <c r="L14" s="1">
         <v>0.96</v>
       </c>
-      <c r="L14" s="1">
-        <v>0.97</v>
-      </c>
       <c r="M14" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="N14" s="1">
         <v>0.98</v>
       </c>
-      <c r="N14" s="1">
-        <v>0.97</v>
-      </c>
       <c r="O14" s="1">
-        <v>0.94</v>
+        <v>0.97</v>
       </c>
       <c r="P14" s="1">
         <v>0.94</v>
       </c>
       <c r="Q14" s="1">
-        <v>0.96</v>
+        <v>0.94</v>
       </c>
       <c r="R14" s="1">
         <v>0.96</v>
       </c>
       <c r="S14" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="T14" s="1">
         <f t="shared" si="0"/>
         <v>0.99</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="25" customHeight="1">
+    <row r="15" spans="1:20" ht="25" customHeight="1">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -31778,48 +31799,48 @@
       <c r="F15" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="1">
+      <c r="H15" s="1">
         <v>0.98</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0.99</v>
       </c>
       <c r="I15" s="1">
         <v>0.99</v>
       </c>
       <c r="J15" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="K15" s="1">
         <v>0.98</v>
       </c>
-      <c r="K15" s="1">
+      <c r="L15" s="1">
         <v>0.96</v>
       </c>
-      <c r="L15" s="1">
-        <v>0.97</v>
-      </c>
       <c r="M15" s="1">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N15" s="1">
+        <v>1</v>
+      </c>
+      <c r="O15" s="1">
         <v>0.99</v>
       </c>
-      <c r="O15" s="1">
+      <c r="P15" s="1">
         <v>0.96</v>
       </c>
-      <c r="P15" s="1">
+      <c r="Q15" s="1">
         <v>0.94</v>
       </c>
-      <c r="Q15" s="1">
-        <v>0.97</v>
-      </c>
       <c r="R15" s="1">
         <v>0.97</v>
       </c>
       <c r="S15" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="T15" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="25" customHeight="1">
+    <row r="16" spans="1:20" ht="25" customHeight="1">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -31838,48 +31859,48 @@
       <c r="F16" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="1">
+      <c r="H16" s="1">
         <v>0.98</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0.99</v>
       </c>
       <c r="I16" s="1">
         <v>0.99</v>
       </c>
       <c r="J16" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="K16" s="1">
         <v>0.98</v>
       </c>
-      <c r="K16" s="1">
+      <c r="L16" s="1">
         <v>0.96</v>
       </c>
-      <c r="L16" s="1">
-        <v>0.97</v>
-      </c>
       <c r="M16" s="1">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N16" s="1">
+        <v>1</v>
+      </c>
+      <c r="O16" s="1">
         <v>0.99</v>
       </c>
-      <c r="O16" s="1">
+      <c r="P16" s="1">
         <v>0.96</v>
       </c>
-      <c r="P16" s="1">
+      <c r="Q16" s="1">
         <v>0.94</v>
       </c>
-      <c r="Q16" s="1">
-        <v>0.97</v>
-      </c>
       <c r="R16" s="1">
         <v>0.97</v>
       </c>
       <c r="S16" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="T16" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="25" customHeight="1">
+    <row r="17" spans="1:20" ht="25" customHeight="1">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -31898,48 +31919,48 @@
       <c r="F17" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="1">
+      <c r="H17" s="1">
         <v>0.98</v>
       </c>
-      <c r="H17" s="1">
+      <c r="I17" s="1">
         <v>0.94</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17" s="1">
         <v>0.99</v>
       </c>
-      <c r="J17" s="1">
+      <c r="K17" s="1">
         <v>0.98</v>
       </c>
-      <c r="K17" s="1">
+      <c r="L17" s="1">
         <v>0.96</v>
       </c>
-      <c r="L17" s="1">
-        <v>0.97</v>
-      </c>
       <c r="M17" s="1">
         <v>0.97</v>
       </c>
       <c r="N17" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="O17" s="1">
         <v>0.99</v>
       </c>
-      <c r="O17" s="1">
+      <c r="P17" s="1">
         <v>0.96</v>
       </c>
-      <c r="P17" s="1">
+      <c r="Q17" s="1">
         <v>0.94</v>
       </c>
-      <c r="Q17" s="1">
-        <v>0.97</v>
-      </c>
       <c r="R17" s="1">
         <v>0.97</v>
       </c>
       <c r="S17" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="T17" s="1">
         <f t="shared" si="0"/>
         <v>0.99</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="25" customHeight="1">
+    <row r="18" spans="1:20" ht="25" customHeight="1">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -31958,48 +31979,48 @@
       <c r="F18" t="s">
         <v>27</v>
       </c>
-      <c r="G18" s="1">
+      <c r="H18" s="1">
         <v>0.98</v>
-      </c>
-      <c r="H18" s="1">
-        <v>0.99</v>
       </c>
       <c r="I18" s="1">
         <v>0.99</v>
       </c>
       <c r="J18" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="K18" s="1">
         <v>0.98</v>
       </c>
-      <c r="K18" s="1">
+      <c r="L18" s="1">
         <v>0.96</v>
       </c>
-      <c r="L18" s="1">
-        <v>0.97</v>
-      </c>
       <c r="M18" s="1">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N18" s="1">
+        <v>1</v>
+      </c>
+      <c r="O18" s="1">
         <v>0.99</v>
       </c>
-      <c r="O18" s="1">
+      <c r="P18" s="1">
         <v>0.96</v>
       </c>
-      <c r="P18" s="1">
+      <c r="Q18" s="1">
         <v>0.94</v>
       </c>
-      <c r="Q18" s="1">
-        <v>0.97</v>
-      </c>
       <c r="R18" s="1">
         <v>0.97</v>
       </c>
       <c r="S18" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="T18" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="25" customHeight="1">
+    <row r="19" spans="1:20" ht="25" customHeight="1">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -32018,48 +32039,48 @@
       <c r="F19" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <v>0.98</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0.99</v>
       </c>
       <c r="I19" s="1">
         <v>0.99</v>
       </c>
       <c r="J19" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="K19" s="1">
         <v>0.98</v>
       </c>
-      <c r="K19" s="1">
+      <c r="L19" s="1">
         <v>0.96</v>
       </c>
-      <c r="L19" s="1">
-        <v>0.97</v>
-      </c>
       <c r="M19" s="1">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N19" s="1">
+        <v>1</v>
+      </c>
+      <c r="O19" s="1">
         <v>0.99</v>
       </c>
-      <c r="O19" s="1">
+      <c r="P19" s="1">
         <v>0.96</v>
       </c>
-      <c r="P19" s="1">
+      <c r="Q19" s="1">
         <v>0.94</v>
       </c>
-      <c r="Q19" s="1">
-        <v>0.97</v>
-      </c>
       <c r="R19" s="1">
         <v>0.97</v>
       </c>
       <c r="S19" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="T19" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="25" customHeight="1">
+    <row r="22" spans="1:20" ht="25" customHeight="1">
       <c r="B22" t="s">
         <v>1</v>
       </c>
@@ -32073,49 +32094,52 @@
         <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G22" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22" t="s">
         <v>6</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>7</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>8</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>12</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
         <v>13</v>
       </c>
-      <c r="L22" t="s">
+      <c r="M22" t="s">
         <v>14</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>15</v>
       </c>
-      <c r="N22" t="s">
+      <c r="O22" t="s">
         <v>16</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>17</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
         <v>21</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R22" t="s">
         <v>22</v>
       </c>
-      <c r="R22" t="s">
+      <c r="S22" t="s">
         <v>23</v>
       </c>
-      <c r="S22" t="s">
+      <c r="T22" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="25" customHeight="1">
+    <row r="23" spans="1:20" ht="25" customHeight="1">
       <c r="B23">
         <v>1</v>
       </c>
@@ -32131,37 +32155,33 @@
       <c r="F23" t="s">
         <v>24</v>
       </c>
-      <c r="G23" s="1" cm="1">
-        <f t="array" ref="G23">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.72</v>
-      </c>
       <c r="H23" s="1" cm="1">
         <f t="array" ref="H23">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="I23" s="1" cm="1">
         <f t="array" ref="I23">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.76</v>
+        <v>0.67</v>
       </c>
       <c r="J23" s="1" cm="1">
         <f t="array" ref="J23">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="K23" s="1" cm="1">
         <f t="array" ref="K23">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="L23" s="1" cm="1">
         <f t="array" ref="L23">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="M23" s="1" cm="1">
         <f t="array" ref="M23">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="N23" s="1" cm="1">
         <f t="array" ref="N23">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="O23" s="1" cm="1">
         <f t="array" ref="O23">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
@@ -32169,22 +32189,26 @@
       </c>
       <c r="P23" s="1" cm="1">
         <f t="array" ref="P23">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="Q23" s="1" cm="1">
         <f t="array" ref="Q23">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="R23" s="1" cm="1">
         <f t="array" ref="R23">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="S23" s="1" cm="1">
         <f t="array" ref="S23">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
+        <v>0.66</v>
+      </c>
+      <c r="T23" s="1" cm="1">
+        <f t="array" ref="T23">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
         <v>0.76</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="25" customHeight="1">
+    <row r="24" spans="1:20" ht="25" customHeight="1">
       <c r="B24">
         <v>1</v>
       </c>
@@ -32200,49 +32224,45 @@
       <c r="F24" t="s">
         <v>24</v>
       </c>
-      <c r="G24" s="1" cm="1">
-        <f t="array" ref="G24">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.66</v>
-      </c>
       <c r="H24" s="1" cm="1">
         <f t="array" ref="H24">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="I24" s="1" cm="1">
         <f t="array" ref="I24">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="J24" s="1" cm="1">
         <f t="array" ref="J24">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.63</v>
+        <v>0.72</v>
       </c>
       <c r="K24" s="1" cm="1">
         <f t="array" ref="K24">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="L24" s="1" cm="1">
         <f t="array" ref="L24">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.61</v>
+        <v>0.73</v>
       </c>
       <c r="M24" s="1" cm="1">
         <f t="array" ref="M24">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="N24" s="1" cm="1">
         <f t="array" ref="N24">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
       <c r="O24" s="1" cm="1">
         <f t="array" ref="O24">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="P24" s="1" cm="1">
         <f t="array" ref="P24">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="Q24" s="1" cm="1">
         <f t="array" ref="Q24">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="R24" s="1" cm="1">
         <f t="array" ref="R24">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
@@ -32250,10 +32270,14 @@
       </c>
       <c r="S24" s="1" cm="1">
         <f t="array" ref="S24">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
+        <v>0.62</v>
+      </c>
+      <c r="T24" s="1" cm="1">
+        <f t="array" ref="T24">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C24,_xlpm.b,$D$2:$D$19=$D24,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
         <v>0.73</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="25" customHeight="1">
+    <row r="25" spans="1:20" ht="25" customHeight="1">
       <c r="B25">
         <v>2</v>
       </c>
@@ -32269,13 +32293,9 @@
       <c r="F25" t="s">
         <v>24</v>
       </c>
-      <c r="G25" s="1" cm="1">
-        <f t="array" ref="G25">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.77</v>
-      </c>
       <c r="H25" s="1" cm="1">
         <f t="array" ref="H25">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="I25" s="1" cm="1">
         <f t="array" ref="I25">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
@@ -32283,46 +32303,50 @@
       </c>
       <c r="J25" s="1" cm="1">
         <f t="array" ref="J25">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.81</v>
+        <v>0.75</v>
       </c>
       <c r="K25" s="1" cm="1">
         <f t="array" ref="K25">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="L25" s="1" cm="1">
         <f t="array" ref="L25">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="M25" s="1" cm="1">
         <f t="array" ref="M25">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="N25" s="1" cm="1">
         <f t="array" ref="N25">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="O25" s="1" cm="1">
         <f t="array" ref="O25">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.81</v>
+        <v>0.77</v>
       </c>
       <c r="P25" s="1" cm="1">
         <f t="array" ref="P25">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.73</v>
+        <v>0.81</v>
       </c>
       <c r="Q25" s="1" cm="1">
         <f t="array" ref="Q25">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="R25" s="1" cm="1">
         <f t="array" ref="R25">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="S25" s="1" cm="1">
         <f t="array" ref="S25">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
+        <v>0.77</v>
+      </c>
+      <c r="T25" s="1" cm="1">
+        <f t="array" ref="T25">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C25,_xlpm.b,$D$2:$D$19=$D25,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
         <v>0.82</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="25" customHeight="1">
+    <row r="26" spans="1:20" ht="25" customHeight="1">
       <c r="B26">
         <v>2</v>
       </c>
@@ -32338,60 +32362,60 @@
       <c r="F26" t="s">
         <v>24</v>
       </c>
-      <c r="G26" s="1" cm="1">
-        <f t="array" ref="G26">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.72</v>
-      </c>
       <c r="H26" s="1" cm="1">
         <f t="array" ref="H26">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="I26" s="1" cm="1">
         <f t="array" ref="I26">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="J26" s="1" cm="1">
         <f t="array" ref="J26">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="K26" s="1" cm="1">
         <f t="array" ref="K26">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="L26" s="1" cm="1">
         <f t="array" ref="L26">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.69</v>
+        <v>0.79</v>
       </c>
       <c r="M26" s="1" cm="1">
         <f t="array" ref="M26">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.68</v>
+        <v>0.69</v>
       </c>
       <c r="N26" s="1" cm="1">
         <f t="array" ref="N26">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.83</v>
+        <v>0.68</v>
       </c>
       <c r="O26" s="1" cm="1">
         <f t="array" ref="O26">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="P26" s="1" cm="1">
         <f t="array" ref="P26">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="Q26" s="1" cm="1">
         <f t="array" ref="Q26">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
       <c r="R26" s="1" cm="1">
         <f t="array" ref="R26">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="S26" s="1" cm="1">
         <f t="array" ref="S26">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
+        <v>0.77</v>
+      </c>
+      <c r="T26" s="1" cm="1">
+        <f t="array" ref="T26">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C26,_xlpm.b,$D$2:$D$19=$D26,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
         <v>0.83</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="25" customHeight="1">
+    <row r="27" spans="1:20" ht="25" customHeight="1">
       <c r="B27">
         <v>3</v>
       </c>
@@ -32407,13 +32431,9 @@
       <c r="F27" t="s">
         <v>24</v>
       </c>
-      <c r="G27" s="1" cm="1">
-        <f t="array" ref="G27">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.98</v>
-      </c>
       <c r="H27" s="1" cm="1">
         <f t="array" ref="H27">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="I27" s="1" cm="1">
         <f t="array" ref="I27">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
@@ -32425,31 +32445,31 @@
       </c>
       <c r="K27" s="1" cm="1">
         <f t="array" ref="K27">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="L27" s="1" cm="1">
         <f t="array" ref="L27">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="M27" s="1" cm="1">
         <f t="array" ref="M27">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N27" s="1" cm="1">
         <f t="array" ref="N27">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="O27" s="1" cm="1">
         <f t="array" ref="O27">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="P27" s="1" cm="1">
         <f t="array" ref="P27">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.94</v>
+        <v>0.96</v>
       </c>
       <c r="Q27" s="1" cm="1">
         <f t="array" ref="Q27">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.97</v>
+        <v>0.94</v>
       </c>
       <c r="R27" s="1" cm="1">
         <f t="array" ref="R27">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
@@ -32457,10 +32477,14 @@
       </c>
       <c r="S27" s="1" cm="1">
         <f t="array" ref="S27">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="25" customHeight="1">
+        <v>0.97</v>
+      </c>
+      <c r="T27" s="1" cm="1">
+        <f t="array" ref="T27">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C27,_xlpm.b,$D$2:$D$19=$D27,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="25" customHeight="1">
       <c r="B28">
         <v>3</v>
       </c>
@@ -32476,13 +32500,9 @@
       <c r="F28" t="s">
         <v>24</v>
       </c>
-      <c r="G28" s="1" cm="1">
-        <f t="array" ref="G28">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.98</v>
-      </c>
       <c r="H28" s="1" cm="1">
         <f t="array" ref="H28">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="I28" s="1" cm="1">
         <f t="array" ref="I28">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
@@ -32490,35 +32510,35 @@
       </c>
       <c r="J28" s="1" cm="1">
         <f t="array" ref="J28">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="K28" s="1" cm="1">
         <f t="array" ref="K28">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="L28" s="1" cm="1">
         <f t="array" ref="L28">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="M28" s="1" cm="1">
         <f t="array" ref="M28">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N28" s="1" cm="1">
         <f t="array" ref="N28">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="O28" s="1" cm="1">
         <f t="array" ref="O28">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="P28" s="1" cm="1">
         <f t="array" ref="P28">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.94</v>
+        <v>0.96</v>
       </c>
       <c r="Q28" s="1" cm="1">
         <f t="array" ref="Q28">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
-        <v>0.97</v>
+        <v>0.94</v>
       </c>
       <c r="R28" s="1" cm="1">
         <f t="array" ref="R28">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
@@ -32526,11 +32546,15 @@
       </c>
       <c r="S28" s="1" cm="1">
         <f t="array" ref="S28">_xlfn.LET(_xlpm.d,S$2:S$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
+        <v>0.97</v>
+      </c>
+      <c r="T28" s="1" cm="1">
+        <f t="array" ref="T28">_xlfn.LET(_xlpm.d,T$2:T$19,_xlpm.a,$C$2:$C$19=$C28,_xlpm.b,$D$2:$D$19=$D28,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</f>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:S19">
+  <conditionalFormatting sqref="H2:T19">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -32542,7 +32566,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23:S28">
+  <conditionalFormatting sqref="H23:T28">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
